--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O63" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="P63" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O64" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P64" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>46186.5</v>
+        <v>46186.45833333334</v>
       </c>
     </row>
     <row r="34">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="AU36" s="3" t="n">
-        <v>46186.54166666666</v>
+        <v>46186.5</v>
       </c>
     </row>
     <row r="37">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O57" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P57" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O58" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P58" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,17 +8830,17 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O55" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O56" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P56" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O56" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P56" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O57" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P57" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O58" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P58" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O63" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P63" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O64" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="P64" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,17 +8830,17 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O54" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P54" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O56" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P56" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O63" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="P63" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O64" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P64" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>9</v>
+        <v>3.71</v>
       </c>
       <c r="P11" t="n">
-        <v>1.05</v>
+        <v>2.92</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,17 +8830,17 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O57" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P57" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O58" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P58" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O63" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P63" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O64" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="P64" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>2.21</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>3.71</v>
       </c>
       <c r="P10" t="n">
-        <v>1.05</v>
+        <v>2.92</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O56" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P56" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N62" t="n">

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU66"/>
+  <dimension ref="A1:AU65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="AU36" s="3" t="n">
-        <v>46186.5</v>
+        <v>46186.54166666666</v>
       </c>
     </row>
     <row r="37">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,14 +6290,14 @@
         </is>
       </c>
       <c r="N37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P37" t="n">
         <v>3.74</v>
       </c>
-      <c r="O37" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.77</v>
-      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="AU37" s="3" t="n">
-        <v>46186.54166666666</v>
+        <v>46186.5625</v>
       </c>
     </row>
     <row r="38">
@@ -6402,12 +6402,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6552,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="AU38" s="3" t="n">
-        <v>46186.5625</v>
+        <v>46186.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6711,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="AU39" s="3" t="n">
-        <v>46186.58333333334</v>
+        <v>46186.625</v>
       </c>
     </row>
     <row r="40">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="AU41" s="3" t="n">
-        <v>46186.625</v>
+        <v>46186.64583333334</v>
       </c>
     </row>
     <row r="42">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AU45" s="3" t="n">
-        <v>46186.64583333334</v>
+        <v>46186.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>46186.66666666666</v>
+        <v>46186.77083333334</v>
       </c>
     </row>
     <row r="51">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="AU51" s="3" t="n">
-        <v>46186.77083333334</v>
+        <v>46186.79166666666</v>
       </c>
     </row>
     <row r="52">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="AU53" s="3" t="n">
-        <v>46186.79166666666</v>
+        <v>46186.83333333334</v>
       </c>
     </row>
     <row r="54">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O54" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P54" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="O56" t="n">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="P56" t="n">
-        <v>3.41</v>
+        <v>4.28</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,11 +9350,11 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB56" t="n">
         <v>2</v>
       </c>
-      <c r="AB56" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC56" t="n">
         <v>0</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="AU56" s="3" t="n">
-        <v>46186.83333333334</v>
+        <v>46186.85416666666</v>
       </c>
     </row>
     <row r="57">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="O58" t="n">
         <v>3.44</v>
       </c>
       <c r="P58" t="n">
-        <v>4.28</v>
+        <v>3.32</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB58" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9732,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="AU58" s="3" t="n">
-        <v>46186.85416666666</v>
+        <v>46186.875</v>
       </c>
     </row>
     <row r="59">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10209,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>46186.875</v>
+        <v>46186.89583333334</v>
       </c>
     </row>
     <row r="62">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>46186.89583333334</v>
+        <v>46186.91666666666</v>
       </c>
     </row>
     <row r="63">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="O64" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="P64" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>46186.91666666666</v>
+        <v>46186.9375</v>
       </c>
     </row>
     <row r="65">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.09</v>
+        <v>1.69</v>
       </c>
       <c r="O65" t="n">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="P65" t="n">
-        <v>3.04</v>
+        <v>4.16</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10845,165 +10845,6 @@
         <v>0</v>
       </c>
       <c r="AU65" s="3" t="n">
-        <v>46186.9375</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>46186</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Oakland Roots</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Miami FC II</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="O66" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="P66" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU66" s="3" t="n">
         <v>46186.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>26</v>
       </c>
       <c r="O11" t="n">
-        <v>3.71</v>
+        <v>9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.92</v>
+        <v>1.05</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O56" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P56" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O57" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P57" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O62" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P62" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O63" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="P63" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O53" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P53" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O54" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P54" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N61" t="n">

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O53" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P53" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O56" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P56" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O57" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P57" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O56" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P56" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O57" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P57" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>26</v>
       </c>
       <c r="O12" t="n">
-        <v>3.71</v>
+        <v>9</v>
       </c>
       <c r="P12" t="n">
-        <v>2.92</v>
+        <v>1.05</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,17 +8512,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O56" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P56" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O57" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P57" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O62" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="P62" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O63" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P63" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>26</v>
       </c>
       <c r="O11" t="n">
-        <v>3.71</v>
+        <v>9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.92</v>
+        <v>1.05</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O55" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P55" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O56" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P56" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O57" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P57" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O55" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O56" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P56" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O57" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P57" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O62" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P62" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O63" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="P63" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,10 +6641,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O55" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P55" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G60" t="n">

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU65"/>
+  <dimension ref="A1:AU67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,10 +6641,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="O41" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="P41" t="n">
-        <v>5.02</v>
+        <v>3.33</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,14 +7085,14 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.17</v>
+        <v>2.32</v>
       </c>
       <c r="O42" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P42" t="n">
         <v>3.3</v>
       </c>
-      <c r="P42" t="n">
-        <v>2.07</v>
-      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.32</v>
+        <v>3.17</v>
       </c>
       <c r="O43" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="O44" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="P44" t="n">
-        <v>3.33</v>
+        <v>5.02</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,10 +8072,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,68 +8194,68 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>46186.77083333334</v>
+        <v>46186.66666666666</v>
       </c>
     </row>
     <row r="51">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="AU51" s="3" t="n">
-        <v>46186.79166666666</v>
+        <v>46186.77083333334</v>
       </c>
     </row>
     <row r="52">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,68 +8830,68 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="AU53" s="3" t="n">
-        <v>46186.83333333334</v>
+        <v>46186.79166666666</v>
       </c>
     </row>
     <row r="54">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,17 +8989,17 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="AU54" s="3" t="n">
-        <v>46186.83333333334</v>
+        <v>46186.79166666666</v>
       </c>
     </row>
     <row r="55">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="O56" t="n">
-        <v>3.44</v>
+        <v>3.34</v>
       </c>
       <c r="P56" t="n">
-        <v>4.28</v>
+        <v>3.41</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,11 +9350,11 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB56" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB56" t="n">
-        <v>2</v>
-      </c>
       <c r="AC56" t="n">
         <v>0</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="AU56" s="3" t="n">
-        <v>46186.85416666666</v>
+        <v>46186.83333333334</v>
       </c>
     </row>
     <row r="57">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="AU57" s="3" t="n">
-        <v>46186.85416666666</v>
+        <v>46186.83333333334</v>
       </c>
     </row>
     <row r="58">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="O58" t="n">
         <v>3.44</v>
       </c>
       <c r="P58" t="n">
-        <v>3.32</v>
+        <v>4.28</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9732,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="AU58" s="3" t="n">
-        <v>46186.875</v>
+        <v>46186.85416666666</v>
       </c>
     </row>
     <row r="59">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AU59" s="3" t="n">
-        <v>46186.875</v>
+        <v>46186.85416666666</v>
       </c>
     </row>
     <row r="60">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -10209,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>46186.89583333334</v>
+        <v>46186.875</v>
       </c>
     </row>
     <row r="62">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>46186.91666666666</v>
+        <v>46186.875</v>
       </c>
     </row>
     <row r="63">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10420,17 +10420,17 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10527,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="AU63" s="3" t="n">
-        <v>46186.91666666666</v>
+        <v>46186.89583333334</v>
       </c>
     </row>
     <row r="64">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="O64" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="P64" t="n">
-        <v>3.04</v>
+        <v>3.26</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>46186.9375</v>
+        <v>46186.91666666666</v>
       </c>
     </row>
     <row r="65">
@@ -10695,156 +10695,474 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Colorado Springs</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P65" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" s="3" t="n">
+        <v>46186.91666666666</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="O66" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="P66" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" s="3" t="n">
+        <v>46186.9375</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Oakland Roots</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Miami FC II</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="inlineStr">
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N65" t="n">
+      <c r="N67" t="n">
         <v>1.69</v>
       </c>
-      <c r="O65" t="n">
+      <c r="O67" t="n">
         <v>3.78</v>
       </c>
-      <c r="P65" t="n">
+      <c r="P67" t="n">
         <v>4.16</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU65" s="3" t="n">
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" s="3" t="n">
         <v>46186.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,10 +6641,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>3.17</v>
       </c>
       <c r="O41" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>3.33</v>
+        <v>2.07</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O42" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="P42" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,14 +7244,14 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.17</v>
+        <v>2.32</v>
       </c>
       <c r="O43" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P43" t="n">
         <v>3.3</v>
       </c>
-      <c r="P43" t="n">
-        <v>2.07</v>
-      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="O46" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="P46" t="n">
-        <v>3.83</v>
+        <v>2.67</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,68 +8035,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.88</v>
+        <v>1.53</v>
       </c>
       <c r="O48" t="n">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="P48" t="n">
-        <v>2.67</v>
+        <v>4.95</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.83</v>
+        <v>1.12</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.93</v>
+        <v>4.65</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,68 +8194,68 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,10 +8390,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O55" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O56" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P56" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.21</v>
+        <v>26</v>
       </c>
       <c r="O13" t="n">
-        <v>3.71</v>
+        <v>9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.92</v>
+        <v>1.05</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,10 +6641,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.17</v>
+        <v>2.4</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="P41" t="n">
-        <v>2.07</v>
+        <v>3.33</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="O42" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="P42" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="O43" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="P43" t="n">
-        <v>3.3</v>
+        <v>5.02</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.85</v>
+        <v>3.17</v>
       </c>
       <c r="O44" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="P44" t="n">
-        <v>5.02</v>
+        <v>2.07</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,68 +8035,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,68 +8194,68 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,10 +8390,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,17 +8830,17 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O55" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P55" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>2.35</v>
       </c>
       <c r="O13" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.05</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,10 +6641,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="O41" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="P41" t="n">
-        <v>3.33</v>
+        <v>5.02</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.85</v>
+        <v>3.17</v>
       </c>
       <c r="O43" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>5.02</v>
+        <v>2.07</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.17</v>
+        <v>2.4</v>
       </c>
       <c r="O44" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="P44" t="n">
-        <v>2.07</v>
+        <v>3.33</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="O45" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="P45" t="n">
-        <v>3.83</v>
+        <v>2.67</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,68 +7717,68 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.88</v>
+        <v>1.53</v>
       </c>
       <c r="O46" t="n">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="P46" t="n">
-        <v>2.67</v>
+        <v>4.95</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.83</v>
+        <v>1.12</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.93</v>
+        <v>4.65</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,10 +8072,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,68 +8194,68 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O64" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="P64" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O65" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P65" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="O10" t="n">
-        <v>3.71</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="O11" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.71</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6.25</v>
+        <v>2.88</v>
       </c>
       <c r="O23" t="n">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>1.38</v>
+        <v>2.35</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.88</v>
+        <v>6.25</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>4.35</v>
       </c>
       <c r="P24" t="n">
-        <v>2.35</v>
+        <v>1.38</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.07</v>
+        <v>6.76</v>
       </c>
       <c r="O33" t="n">
-        <v>3.54</v>
+        <v>4.4</v>
       </c>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.32</v>
+        <v>3.17</v>
       </c>
       <c r="O42" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,14 +7244,14 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.17</v>
+        <v>2.32</v>
       </c>
       <c r="O43" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P43" t="n">
         <v>3.3</v>
       </c>
-      <c r="P43" t="n">
-        <v>2.07</v>
-      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="O45" t="n">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="P45" t="n">
-        <v>2.67</v>
+        <v>3.83</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,68 +7717,68 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,10 +8072,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,68 +8353,68 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,68 +8830,68 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="O53" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="P53" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O55" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O57" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P57" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O58" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P58" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O59" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P59" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.02</v>
+        <v>1.42</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>5.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.35</v>
+        <v>26</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>1.05</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>26</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>3.71</v>
       </c>
       <c r="P12" t="n">
-        <v>1.05</v>
+        <v>2.92</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="O13" t="n">
-        <v>3.71</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>2.95</v>
       </c>
       <c r="P15" t="n">
-        <v>2.41</v>
+        <v>3.75</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="O21" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O43" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="P43" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="O44" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="P44" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,68 +8194,68 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,68 +8353,68 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,17 +8989,17 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O55" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P55" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O57" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P57" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O58" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P58" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O59" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P59" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O64" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P64" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O65" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="P65" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="O4" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.85</v>
+        <v>5.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>3.71</v>
       </c>
       <c r="P10" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="O12" t="n">
-        <v>3.71</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.88</v>
+        <v>4.59</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>4.11</v>
       </c>
       <c r="P23" t="n">
-        <v>2.35</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.59</v>
+        <v>2.88</v>
       </c>
       <c r="O25" t="n">
-        <v>4.11</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.07</v>
+        <v>6.76</v>
       </c>
       <c r="O32" t="n">
-        <v>3.54</v>
+        <v>4.4</v>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,10 +6641,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="O41" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="P41" t="n">
-        <v>5.02</v>
+        <v>3.33</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.17</v>
+        <v>1.85</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="P42" t="n">
-        <v>2.07</v>
+        <v>5.02</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="O43" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="P43" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.32</v>
+        <v>3.17</v>
       </c>
       <c r="O44" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="P44" t="n">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,69 +7558,69 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O45" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG45" t="n">
         <v>2.1</v>
       </c>
-      <c r="O45" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="P45" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
       <c r="AH45" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,10 +8072,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,68 +8194,68 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="O49" t="n">
-        <v>4.1</v>
+        <v>2.76</v>
       </c>
       <c r="P49" t="n">
-        <v>4.95</v>
+        <v>3.83</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.12</v>
+        <v>1.6</v>
       </c>
       <c r="Z49" t="n">
-        <v>4.65</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,64 +8675,64 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,68 +8830,68 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O55" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O57" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P57" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O58" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P58" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O59" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P59" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O64" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="P64" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O65" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P65" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>5.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.85</v>
+        <v>5.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="O10" t="n">
-        <v>3.71</v>
+        <v>3.45</v>
       </c>
       <c r="P10" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.71</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="O17" t="n">
-        <v>3.54</v>
+        <v>2.95</v>
       </c>
       <c r="P17" t="n">
-        <v>2.41</v>
+        <v>3.75</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.59</v>
+        <v>2.88</v>
       </c>
       <c r="O23" t="n">
-        <v>4.11</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>6.25</v>
+        <v>4.59</v>
       </c>
       <c r="O24" t="n">
-        <v>4.35</v>
+        <v>4.11</v>
       </c>
       <c r="P24" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.88</v>
+        <v>6.25</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>4.35</v>
       </c>
       <c r="P25" t="n">
-        <v>2.35</v>
+        <v>1.38</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.07</v>
+        <v>6.76</v>
       </c>
       <c r="O31" t="n">
-        <v>3.54</v>
+        <v>4.4</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,10 +6641,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="O41" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="P41" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.32</v>
+        <v>3.17</v>
       </c>
       <c r="O43" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="P43" t="n">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.17</v>
+        <v>2.4</v>
       </c>
       <c r="O44" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="P44" t="n">
-        <v>2.07</v>
+        <v>3.33</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,68 +7558,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.53</v>
+        <v>2.88</v>
       </c>
       <c r="O45" t="n">
-        <v>4.1</v>
+        <v>2.58</v>
       </c>
       <c r="P45" t="n">
-        <v>4.95</v>
+        <v>2.67</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.12</v>
+        <v>1.83</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.65</v>
+        <v>1.93</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,10 +8072,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,69 +8194,69 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O49" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG49" t="n">
         <v>2.1</v>
       </c>
-      <c r="O49" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="P49" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,10 +8390,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,68 +8671,68 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,68 +8989,68 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="O54" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="P54" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O55" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P55" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G62" t="n">

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.85</v>
+        <v>5.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>5.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.06</v>
+        <v>26</v>
       </c>
       <c r="O10" t="n">
-        <v>3.45</v>
+        <v>9</v>
       </c>
       <c r="P10" t="n">
-        <v>2.95</v>
+        <v>1.05</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>9</v>
+        <v>3.71</v>
       </c>
       <c r="P11" t="n">
-        <v>1.05</v>
+        <v>2.92</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="O12" t="n">
-        <v>3.71</v>
+        <v>3.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="O17" t="n">
-        <v>2.95</v>
+        <v>3.54</v>
       </c>
       <c r="P17" t="n">
-        <v>3.75</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.07</v>
+        <v>6.76</v>
       </c>
       <c r="O30" t="n">
-        <v>3.54</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.49</v>
+        <v>1.97</v>
       </c>
       <c r="O39" t="n">
-        <v>2.72</v>
+        <v>3.55</v>
       </c>
       <c r="P39" t="n">
-        <v>3.03</v>
+        <v>3.29</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,10 +6641,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,16 +6800,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="O42" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="P42" t="n">
-        <v>5.02</v>
+        <v>3.33</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,16 +7118,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="O44" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="P44" t="n">
-        <v>3.33</v>
+        <v>5.02</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,16 +7436,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,68 +7558,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>1.53</v>
       </c>
       <c r="O45" t="n">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="P45" t="n">
-        <v>2.67</v>
+        <v>4.95</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.83</v>
+        <v>1.12</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.93</v>
+        <v>4.65</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,16 +8072,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,68 +8194,68 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>2.2</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,68 +8830,68 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="O53" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="P53" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,68 +8989,68 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="O54" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="P54" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O58" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P58" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O59" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P59" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O64" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P64" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O65" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="P65" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="O5" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.85</v>
+        <v>5.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="O11" t="n">
-        <v>3.71</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="O12" t="n">
-        <v>3.45</v>
+        <v>3.71</v>
       </c>
       <c r="P12" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.41</v>
+        <v>3.15</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.88</v>
+        <v>6.25</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>4.35</v>
       </c>
       <c r="P23" t="n">
-        <v>2.35</v>
+        <v>1.38</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.59</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
-        <v>4.11</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>6.25</v>
+        <v>4.59</v>
       </c>
       <c r="O25" t="n">
-        <v>4.35</v>
+        <v>4.11</v>
       </c>
       <c r="P25" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>6.76</v>
+        <v>2.07</v>
       </c>
       <c r="O30" t="n">
-        <v>4.4</v>
+        <v>3.54</v>
       </c>
       <c r="P30" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O41" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="P41" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>2.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="O42" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="P42" t="n">
-        <v>3.33</v>
+        <v>5.02</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,16 +7118,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="O44" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="P44" t="n">
-        <v>5.02</v>
+        <v>3.3</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,16 +7436,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,68 +7558,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="O45" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="P45" t="n">
-        <v>4.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="O46" t="n">
-        <v>3.25</v>
+        <v>2.58</v>
       </c>
       <c r="P46" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,16 +7754,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,16 +7913,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,68 +8035,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.88</v>
+        <v>1.53</v>
       </c>
       <c r="O48" t="n">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="P48" t="n">
-        <v>2.67</v>
+        <v>4.95</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.83</v>
+        <v>1.12</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.93</v>
+        <v>4.65</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.28</v>
+        <v>2.32</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,16 +8390,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,68 +8830,68 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="O53" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="P53" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,68 +8989,68 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="O54" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="P54" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O58" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P58" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB58" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O59" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P59" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="O61" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P61" t="n">
-        <v>3.32</v>
+        <v>4.05</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.02</v>
+        <v>1.42</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="O12" t="n">
-        <v>3.71</v>
+        <v>3.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.71</v>
       </c>
       <c r="P13" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="O22" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6.25</v>
+        <v>2.88</v>
       </c>
       <c r="O23" t="n">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>1.38</v>
+        <v>2.35</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.88</v>
+        <v>6.25</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>4.35</v>
       </c>
       <c r="P24" t="n">
-        <v>2.35</v>
+        <v>1.38</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.07</v>
+        <v>6.76</v>
       </c>
       <c r="O30" t="n">
-        <v>3.54</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.85</v>
+        <v>3.17</v>
       </c>
       <c r="O42" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>5.02</v>
+        <v>2.07</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,16 +7118,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,14 +7244,14 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.17</v>
+        <v>2.32</v>
       </c>
       <c r="O43" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P43" t="n">
         <v>3.3</v>
       </c>
-      <c r="P43" t="n">
-        <v>2.07</v>
-      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="O44" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="P44" t="n">
-        <v>3.3</v>
+        <v>5.02</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,16 +7436,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,17 +7558,17 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="O53" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="P53" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O57" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P57" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O58" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P58" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O59" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P59" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O64" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="P64" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O65" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P65" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="O12" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="P12" t="n">
-        <v>2.95</v>
+        <v>4.15</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="O13" t="n">
-        <v>3.71</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.41</v>
+        <v>3.15</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>6.25</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>1.38</v>
+        <v>2.35</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.59</v>
+        <v>6.25</v>
       </c>
       <c r="O25" t="n">
-        <v>4.11</v>
+        <v>4.35</v>
       </c>
       <c r="P25" t="n">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>6.76</v>
+        <v>2.07</v>
       </c>
       <c r="O30" t="n">
-        <v>4.4</v>
+        <v>3.54</v>
       </c>
       <c r="P30" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.97</v>
+        <v>2.49</v>
       </c>
       <c r="O39" t="n">
-        <v>3.55</v>
+        <v>2.72</v>
       </c>
       <c r="P39" t="n">
-        <v>3.29</v>
+        <v>3.03</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,16 +6641,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.49</v>
+        <v>1.97</v>
       </c>
       <c r="O40" t="n">
-        <v>2.72</v>
+        <v>3.55</v>
       </c>
       <c r="P40" t="n">
-        <v>3.03</v>
+        <v>3.29</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,16 +6800,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="O41" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="P41" t="n">
-        <v>3.33</v>
+        <v>5.02</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,16 +6959,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,14 +7085,14 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.17</v>
+        <v>2.32</v>
       </c>
       <c r="O42" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P42" t="n">
         <v>3.3</v>
       </c>
-      <c r="P42" t="n">
-        <v>2.07</v>
-      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O43" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="P43" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7283,10 +7283,10 @@
         <v>2.1</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.85</v>
+        <v>3.17</v>
       </c>
       <c r="O44" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="P44" t="n">
-        <v>5.02</v>
+        <v>2.07</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,16 +7436,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,17 +7558,17 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,16 +7913,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,16 +8231,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O55" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O57" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P57" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,49 +10106,49 @@
         </is>
       </c>
       <c r="N61" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O61" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P61" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB61" t="n">
         <v>1.91</v>
-      </c>
-      <c r="O61" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P61" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1.85</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="O8" t="n">
         <v>3.5</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>4.15</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="O12" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>4.15</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.51</v>
+        <v>2.88</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.88</v>
+        <v>6.25</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>4.35</v>
       </c>
       <c r="P24" t="n">
-        <v>2.35</v>
+        <v>1.38</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>6.25</v>
+        <v>2.51</v>
       </c>
       <c r="O25" t="n">
-        <v>4.35</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.38</v>
+        <v>2.65</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.07</v>
+        <v>6.76</v>
       </c>
       <c r="O30" t="n">
-        <v>3.54</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="O35" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="P35" t="n">
-        <v>7.19</v>
+        <v>5.96</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.85</v>
+        <v>3.17</v>
       </c>
       <c r="O41" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="P41" t="n">
-        <v>5.02</v>
+        <v>2.07</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,16 +6959,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O42" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="P42" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>2.1</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="O43" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="P43" t="n">
-        <v>3.33</v>
+        <v>5.02</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,16 +7277,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,14 +7403,14 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.17</v>
+        <v>2.32</v>
       </c>
       <c r="O44" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P44" t="n">
         <v>3.3</v>
       </c>
-      <c r="P44" t="n">
-        <v>2.07</v>
-      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,16 +7754,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,68 +8035,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,16 +8390,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,17 +8989,17 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O55" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P55" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O57" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P57" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="O61" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="P61" t="n">
-        <v>3.32</v>
+        <v>4.05</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,49 +10265,49 @@
         </is>
       </c>
       <c r="N62" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O62" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P62" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB62" t="n">
         <v>1.91</v>
-      </c>
-      <c r="O62" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P62" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>1.85</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O64" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P64" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O65" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="P65" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.85</v>
+        <v>5.4</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>5.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P9" t="n">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>22</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
-        <v>8.4</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.07</v>
+        <v>3.03</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="O11" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="P11" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>4.15</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.06</v>
+        <v>22</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>8.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.95</v>
+        <v>1.07</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P17" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.51</v>
+        <v>2.88</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="O29" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>6.76</v>
+        <v>2.11</v>
       </c>
       <c r="O30" t="n">
-        <v>4.4</v>
+        <v>3.54</v>
       </c>
       <c r="P30" t="n">
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.49</v>
+        <v>1.97</v>
       </c>
       <c r="O39" t="n">
-        <v>2.72</v>
+        <v>3.55</v>
       </c>
       <c r="P39" t="n">
-        <v>3.03</v>
+        <v>3.29</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,16 +6641,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.97</v>
+        <v>2.49</v>
       </c>
       <c r="O40" t="n">
-        <v>3.55</v>
+        <v>2.72</v>
       </c>
       <c r="P40" t="n">
-        <v>3.29</v>
+        <v>3.03</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,16 +6800,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.17</v>
+        <v>1.85</v>
       </c>
       <c r="O41" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="P41" t="n">
-        <v>2.07</v>
+        <v>5.02</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,16 +6959,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.4</v>
+        <v>3.17</v>
       </c>
       <c r="O42" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="P42" t="n">
-        <v>3.33</v>
+        <v>2.07</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,16 +7118,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="O43" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="P43" t="n">
-        <v>5.02</v>
+        <v>3.3</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,16 +7277,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O44" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="P44" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7442,10 +7442,10 @@
         <v>2.1</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,17 +8035,17 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,16 +8072,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,65 +8198,65 @@
         </is>
       </c>
       <c r="N49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O49" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG49" t="n">
         <v>2.1</v>
       </c>
-      <c r="O49" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="P49" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="O50" t="n">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="P50" t="n">
-        <v>2.67</v>
+        <v>3.83</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,16 +8390,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,68 +8830,68 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="O54" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="P54" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>1.97</v>
       </c>
       <c r="O55" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>3.41</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O57" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="P57" t="n">
-        <v>3.41</v>
+        <v>2.63</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O58" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P58" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB58" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O59" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P59" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P10" t="n">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.81</v>
+        <v>22</v>
       </c>
       <c r="O12" t="n">
-        <v>3.48</v>
+        <v>8.4</v>
       </c>
       <c r="P12" t="n">
-        <v>4.15</v>
+        <v>1.07</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>22</v>
+        <v>1.81</v>
       </c>
       <c r="O13" t="n">
-        <v>8.4</v>
+        <v>3.48</v>
       </c>
       <c r="P13" t="n">
-        <v>1.07</v>
+        <v>4.15</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="O16" t="n">
-        <v>3.54</v>
+        <v>2.95</v>
       </c>
       <c r="P16" t="n">
-        <v>2.41</v>
+        <v>3.75</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.51</v>
+        <v>6.25</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>4.35</v>
       </c>
       <c r="P23" t="n">
-        <v>2.65</v>
+        <v>1.38</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>6.25</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
-        <v>4.35</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>1.38</v>
+        <v>2.35</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>6.76</v>
+        <v>1.83</v>
       </c>
       <c r="O33" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="P33" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="O40" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="P40" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="O41" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="P41" t="n">
-        <v>5.02</v>
+        <v>3.3</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,16 +6959,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="O43" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="P43" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7283,10 +7283,10 @@
         <v>2.1</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="O44" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P44" t="n">
-        <v>3.33</v>
+        <v>4.33</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,16 +7436,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,17 +7717,17 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,16 +7754,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="O48" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="P48" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,16 +8390,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8993,43 +8993,43 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="O54" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P54" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.51</v>
+        <v>3</v>
       </c>
       <c r="R54" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="S54" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T54" t="n">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="U54" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="V54" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W54" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X54" t="n">
         <v>1.02</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z54" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AA54" t="n">
         <v>1.48</v>
@@ -9038,19 +9038,19 @@
         <v>2.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AD54" t="n">
         <v>1.64</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="O58" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="P58" t="n">
-        <v>6.81</v>
+        <v>4.28</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB58" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="O59" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="P59" t="n">
-        <v>4.28</v>
+        <v>6.81</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.88</v>
+        <v>3.41</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="O4" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>5.4</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.02</v>
+        <v>1.49</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>6.05</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="O8" t="n">
         <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>22</v>
+        <v>1.81</v>
       </c>
       <c r="O12" t="n">
-        <v>8.4</v>
+        <v>3.44</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>4.1</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.81</v>
+        <v>22</v>
       </c>
       <c r="O13" t="n">
-        <v>3.48</v>
+        <v>8.4</v>
       </c>
       <c r="P13" t="n">
-        <v>4.15</v>
+        <v>1.07</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6.25</v>
+        <v>2.45</v>
       </c>
       <c r="O23" t="n">
-        <v>4.35</v>
+        <v>3.44</v>
       </c>
       <c r="P23" t="n">
-        <v>1.38</v>
+        <v>2.73</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.51</v>
+        <v>6.38</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.65</v>
+        <v>1.42</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>6.76</v>
+        <v>1.8</v>
       </c>
       <c r="O31" t="n">
-        <v>4.4</v>
+        <v>3.18</v>
       </c>
       <c r="P31" t="n">
-        <v>1.4</v>
+        <v>4.34</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P33" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>3.74</v>
+        <v>3.61</v>
       </c>
       <c r="O36" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="P36" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="O37" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P37" t="n">
-        <v>3.74</v>
+        <v>4.4</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.17</v>
+        <v>2.4</v>
       </c>
       <c r="O42" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="P42" t="n">
-        <v>2.07</v>
+        <v>3.32</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,16 +7118,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O43" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="P43" t="n">
-        <v>3.32</v>
+        <v>2.62</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,16 +7277,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="O45" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="P45" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,16 +7595,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA45" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="P47" t="n">
-        <v>5</v>
+        <v>2.57</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.83</v>
+        <v>1.83</v>
       </c>
       <c r="O48" t="n">
-        <v>2.57</v>
+        <v>3.05</v>
       </c>
       <c r="P48" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,16 +8072,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8519,7 +8519,7 @@
         <v>1.25</v>
       </c>
       <c r="O51" t="n">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="P51" t="n">
         <v>8.5</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="O52" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="P52" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,68 +8830,68 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,68 +8989,68 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.97</v>
+        <v>4.25</v>
       </c>
       <c r="O56" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P56" t="n">
-        <v>3.41</v>
+        <v>1.72</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="O57" t="n">
-        <v>3.22</v>
+        <v>2.87</v>
       </c>
       <c r="P57" t="n">
-        <v>2.63</v>
+        <v>3.93</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O58" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="P58" t="n">
-        <v>4.28</v>
+        <v>4.4</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="O59" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P59" t="n">
-        <v>6.81</v>
+        <v>6.28</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="O60" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P60" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="O62" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="P62" t="n">
-        <v>4.05</v>
+        <v>9</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="O64" t="n">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="P64" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="O65" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="P65" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="O66" t="n">
-        <v>3.42</v>
+        <v>3.26</v>
       </c>
       <c r="P66" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O67" t="n">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="P67" t="n">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU67"/>
+  <dimension ref="A1:AU68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="O2" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P2" t="n">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P3" t="n">
-        <v>3.41</v>
+        <v>3.06</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,14 +1043,14 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="O4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P4" t="n">
         <v>3.4</v>
       </c>
-      <c r="P4" t="n">
-        <v>3.01</v>
-      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="O5" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P5" t="n">
-        <v>6.05</v>
+        <v>5.65</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.09</v>
+        <v>4.36</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="O10" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P11" t="n">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.81</v>
+        <v>22</v>
       </c>
       <c r="O12" t="n">
-        <v>3.44</v>
+        <v>8.4</v>
       </c>
       <c r="P12" t="n">
-        <v>4.1</v>
+        <v>1.07</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>22</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>8.4</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.07</v>
+        <v>3.03</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="O23" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.73</v>
+        <v>2.35</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.88</v>
+        <v>6.38</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.35</v>
+        <v>1.42</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>6.38</v>
+        <v>2.45</v>
       </c>
       <c r="O25" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="P25" t="n">
-        <v>1.42</v>
+        <v>2.73</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>6.76</v>
+        <v>1.8</v>
       </c>
       <c r="O30" t="n">
-        <v>4.4</v>
+        <v>3.18</v>
       </c>
       <c r="P30" t="n">
-        <v>1.4</v>
+        <v>4.34</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.8</v>
+        <v>6.76</v>
       </c>
       <c r="O31" t="n">
-        <v>3.18</v>
+        <v>4.4</v>
       </c>
       <c r="P31" t="n">
-        <v>4.34</v>
+        <v>1.4</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -6561,12 +6561,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="O39" t="n">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="P39" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,16 +6641,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6711,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="AU39" s="3" t="n">
-        <v>46186.625</v>
+        <v>46186.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.32</v>
+        <v>1.97</v>
       </c>
       <c r="O41" t="n">
-        <v>2.74</v>
+        <v>3.55</v>
       </c>
       <c r="P41" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="AU41" s="3" t="n">
-        <v>46186.64583333334</v>
+        <v>46186.625</v>
       </c>
     </row>
     <row r="42">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="P42" t="n">
-        <v>3.32</v>
+        <v>2.62</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,16 +7118,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.37</v>
+        <v>3.23</v>
       </c>
       <c r="O43" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="P43" t="n">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,16 +7277,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="O44" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="P44" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,16 +7436,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.83</v>
+        <v>1.52</v>
       </c>
       <c r="O45" t="n">
-        <v>2.57</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.83</v>
+        <v>1.14</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.93</v>
+        <v>4.65</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.6</v>
+        <v>1.54</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.28</v>
+        <v>2.35</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,17 +7717,17 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,16 +7754,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,49 +8039,49 @@
         </is>
       </c>
       <c r="N48" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
         <v>1.83</v>
       </c>
-      <c r="O48" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="P48" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="P49" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,16 +8390,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>46186.66666666666</v>
+        <v>46186.70833333334</v>
       </c>
     </row>
     <row r="51">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="O53" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P53" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="Q53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,68 +8989,68 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>4.25</v>
+        <v>1.9</v>
       </c>
       <c r="O56" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P56" t="n">
-        <v>1.72</v>
+        <v>4.2</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9344,10 +9344,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2</v>
+        <v>4.25</v>
       </c>
       <c r="O57" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="P57" t="n">
-        <v>3.93</v>
+        <v>1.72</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,50 +9629,50 @@
         </is>
       </c>
       <c r="N58" t="n">
+        <v>2</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P58" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB58" t="n">
         <v>1.7</v>
       </c>
-      <c r="O58" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P58" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>2</v>
-      </c>
       <c r="AC58" t="n">
         <v>0</v>
       </c>
@@ -9732,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="AU58" s="3" t="n">
-        <v>46186.85416666666</v>
+        <v>46186.83333333334</v>
       </c>
     </row>
     <row r="59">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="O59" t="n">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="P59" t="n">
-        <v>6.28</v>
+        <v>4.4</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="O60" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P60" t="n">
-        <v>3.6</v>
+        <v>6.28</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,11 +9986,11 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB60" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB60" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC60" t="n">
         <v>0</v>
       </c>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="AU60" s="3" t="n">
-        <v>46186.875</v>
+        <v>46186.85416666666</v>
       </c>
     </row>
     <row r="61">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="O61" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="P61" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="O62" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="P62" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10377,12 +10377,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10420,17 +10420,17 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10527,7 +10527,7 @@
         <v>0</v>
       </c>
       <c r="AU63" s="3" t="n">
-        <v>46186.89583333334</v>
+        <v>46186.875</v>
       </c>
     </row>
     <row r="64">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10579,17 +10579,17 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>46186.91666666666</v>
+        <v>46186.89583333334</v>
       </c>
     </row>
     <row r="65">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="O66" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="P66" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11004,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="AU66" s="3" t="n">
-        <v>46186.9375</v>
+        <v>46186.91666666666</v>
       </c>
     </row>
     <row r="67">
@@ -11013,156 +11013,315 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O67" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" s="3" t="n">
+        <v>46186.9375</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Oakland Roots</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Miami FC II</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="inlineStr">
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N67" t="n">
+      <c r="N68" t="n">
         <v>1.67</v>
       </c>
-      <c r="O67" t="n">
+      <c r="O68" t="n">
         <v>3.85</v>
       </c>
-      <c r="P67" t="n">
+      <c r="P68" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="n">
-        <v>0</v>
-      </c>
-      <c r="W67" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA67" t="n">
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
         <v>1.6</v>
       </c>
-      <c r="AB67" t="n">
+      <c r="AB68" t="n">
         <v>2.3</v>
       </c>
-      <c r="AC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP67" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU67" s="3" t="n">
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" s="3" t="n">
         <v>46186.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P3" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>22</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>8.4</v>
+        <v>3.35</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>22</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>8.4</v>
       </c>
       <c r="P13" t="n">
-        <v>3.03</v>
+        <v>1.07</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.88</v>
+        <v>6.38</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.35</v>
+        <v>1.42</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>6.38</v>
+        <v>2.45</v>
       </c>
       <c r="O24" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="P24" t="n">
-        <v>1.42</v>
+        <v>2.73</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="O25" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.73</v>
+        <v>2.35</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.62</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P29" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.8</v>
+        <v>6.76</v>
       </c>
       <c r="O30" t="n">
-        <v>3.18</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>4.34</v>
+        <v>1.4</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="O33" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="P33" t="n">
-        <v>2.75</v>
+        <v>4.34</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6482,16 +6482,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,16 +6641,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="O40" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="P40" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,16 +6800,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="O41" t="n">
-        <v>3.55</v>
+        <v>2.62</v>
       </c>
       <c r="P41" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,16 +6959,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>3.23</v>
       </c>
       <c r="O42" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="P42" t="n">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,16 +7118,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.23</v>
+        <v>2.37</v>
       </c>
       <c r="O43" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="P43" t="n">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,16 +7277,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,17 +7717,17 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="O47" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="P47" t="n">
-        <v>2.57</v>
+        <v>4.4</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,17 +8194,17 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="O53" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P53" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,68 +8989,68 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>4.25</v>
       </c>
       <c r="O55" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>1.72</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.9</v>
+        <v>2.39</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="P56" t="n">
-        <v>4.2</v>
+        <v>2.63</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9344,16 +9344,16 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>4.25</v>
+        <v>1.9</v>
       </c>
       <c r="O57" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P57" t="n">
-        <v>1.72</v>
+        <v>4.2</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O62" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P62" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB62" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,49 +10424,49 @@
         </is>
       </c>
       <c r="N63" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P63" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB63" t="n">
         <v>2</v>
-      </c>
-      <c r="O63" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P63" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="O65" t="n">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="P65" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="O66" t="n">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
       <c r="P66" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="P2" t="n">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="O3" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="P3" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="O4" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="P4" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O5" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="P7" t="n">
         <v>1.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.81</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>4.1</v>
+        <v>3.03</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P11" t="n">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P12" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="P17" t="n">
-        <v>3.15</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6.38</v>
+        <v>2.45</v>
       </c>
       <c r="O23" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="P23" t="n">
-        <v>1.42</v>
+        <v>2.73</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.45</v>
+        <v>6.38</v>
       </c>
       <c r="O24" t="n">
-        <v>3.44</v>
+        <v>4.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.73</v>
+        <v>1.42</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>6.76</v>
+        <v>1.62</v>
       </c>
       <c r="O30" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="P30" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.62</v>
+        <v>6.76</v>
       </c>
       <c r="O32" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="P32" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6482,16 +6482,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,16 +6641,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="O40" t="n">
-        <v>3.55</v>
+        <v>2.62</v>
       </c>
       <c r="P40" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,16 +6800,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="O41" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="P41" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,16 +6959,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.23</v>
+        <v>2.32</v>
       </c>
       <c r="O42" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="P42" t="n">
-        <v>2.29</v>
+        <v>3.3</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,16 +7118,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.32</v>
+        <v>3.23</v>
       </c>
       <c r="O44" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="P44" t="n">
-        <v>3.3</v>
+        <v>2.29</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,16 +7436,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="P45" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,17 +7717,17 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="O47" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,14 +8039,14 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="O48" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="P48" t="n">
         <v>2.57</v>
       </c>
-      <c r="P48" t="n">
-        <v>2.8</v>
-      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
@@ -8072,16 +8072,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,17 +8194,17 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,16 +8231,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>4.25</v>
+        <v>2</v>
       </c>
       <c r="O55" t="n">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="P55" t="n">
-        <v>1.72</v>
+        <v>3.93</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.9</v>
+        <v>4.25</v>
       </c>
       <c r="O57" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P57" t="n">
-        <v>4.2</v>
+        <v>1.72</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O58" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P58" t="n">
-        <v>3.93</v>
+        <v>4.2</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9662,16 +9662,16 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="O59" t="n">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="P59" t="n">
-        <v>4.4</v>
+        <v>6.28</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="O60" t="n">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="P60" t="n">
-        <v>6.28</v>
+        <v>4.4</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="O61" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="P61" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="O62" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="P62" t="n">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P63" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB63" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="O5" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -2318,61 +2318,61 @@
         <v>1.81</v>
       </c>
       <c r="O12" t="n">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="P12" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>3.15</v>
+        <v>2.41</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.45</v>
+        <v>6.38</v>
       </c>
       <c r="O23" t="n">
-        <v>3.44</v>
+        <v>4.3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.73</v>
+        <v>1.42</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>6.38</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>1.42</v>
+        <v>2.35</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U25" t="n">
         <v>2.88</v>
       </c>
-      <c r="O25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4868,55 +4868,55 @@
         <v>7.47</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="O30" t="n">
-        <v>3.7</v>
+        <v>3.16</v>
       </c>
       <c r="P30" t="n">
-        <v>4.5</v>
+        <v>4.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="O31" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P31" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="O33" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="P33" t="n">
-        <v>4.34</v>
+        <v>2.75</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="O40" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="P40" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,16 +6800,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="O41" t="n">
-        <v>3.55</v>
+        <v>2.62</v>
       </c>
       <c r="P41" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,16 +6959,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="P42" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.37</v>
+        <v>3.23</v>
       </c>
       <c r="O43" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="P43" t="n">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,16 +7277,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.23</v>
+        <v>2.32</v>
       </c>
       <c r="O44" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="P44" t="n">
-        <v>2.29</v>
+        <v>3.3</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,16 +7436,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,17 +7558,17 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,17 +7717,17 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7889,16 +7889,16 @@
         <v>5</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R47" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S47" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T47" t="n">
-        <v>3.75</v>
+        <v>3.32</v>
       </c>
       <c r="U47" t="n">
         <v>2.27</v>
@@ -7907,53 +7907,53 @@
         <v>1.53</v>
       </c>
       <c r="W47" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X47" t="n">
         <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z47" t="n">
         <v>4.65</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB47" t="n">
         <v>2.35</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE47" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47" t="n">
         <v>1.17</v>
       </c>
-      <c r="AF47" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AK47" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="O48" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="P48" t="n">
-        <v>2.57</v>
+        <v>4.35</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA48" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8714,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="O53" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P53" t="n">
         <v>2.05</v>
       </c>
       <c r="Q53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
         <v>2.35</v>
       </c>
       <c r="S53" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T53" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U53" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V53" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W53" t="n">
         <v>1.17</v>
       </c>
       <c r="X53" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y53" t="n">
         <v>1.09</v>
       </c>
       <c r="Z53" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AD53" t="n">
         <v>1.64</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,17 +8989,17 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>4.25</v>
+        <v>1.9</v>
       </c>
       <c r="O57" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P57" t="n">
-        <v>1.72</v>
+        <v>4.2</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>1.9</v>
+        <v>4.25</v>
       </c>
       <c r="O58" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P58" t="n">
-        <v>4.2</v>
+        <v>1.72</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9662,10 +9662,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="O61" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="P61" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="O62" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="P62" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="O65" t="n">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
       <c r="P65" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="O66" t="n">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="P66" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="O4" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1379,13 +1379,13 @@
         <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W6" t="n">
         <v>1.11</v>
@@ -1400,10 +1400,10 @@
         <v>5.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AC6" t="n">
         <v>2.19</v>
@@ -1415,10 +1415,10 @@
         <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
         <v>2.29</v>
@@ -1547,7 +1547,7 @@
         <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
@@ -1565,16 +1565,16 @@
         <v>2.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AE7" t="n">
         <v>1.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
         <v>2.22</v>
@@ -1685,37 +1685,37 @@
         <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
         <v>1.61</v>
@@ -1724,19 +1724,19 @@
         <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="O9" t="n">
         <v>3.55</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>9.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>3.03</v>
+        <v>1.17</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="O11" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>4.27</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="P12" t="n">
-        <v>4.27</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.96</v>
+        <v>2.38</v>
       </c>
       <c r="V12" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.97</v>
+        <v>3.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>22</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>8.4</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.07</v>
+        <v>3.03</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.41</v>
+        <v>3.15</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6.38</v>
+        <v>2.52</v>
       </c>
       <c r="O23" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="P23" t="n">
-        <v>1.42</v>
+        <v>2.65</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,19 +4223,19 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.88</v>
+        <v>6.38</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.35</v>
+        <v>1.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -4244,10 +4244,10 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -4256,31 +4256,31 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="O25" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.65</v>
+        <v>2.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -4562,10 +4562,10 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4574,31 +4574,31 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4709,55 +4709,55 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,19 +5018,19 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>6.76</v>
+        <v>1.67</v>
       </c>
       <c r="O29" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="P29" t="n">
-        <v>1.4</v>
+        <v>4.53</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -5039,10 +5039,10 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -5051,31 +5051,31 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.82</v>
+        <v>6.76</v>
       </c>
       <c r="O30" t="n">
-        <v>3.16</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>4.24</v>
+        <v>1.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="S30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="V30" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.56</v>
+        <v>4.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.29</v>
+        <v>1.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.54</v>
+        <v>2.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.8</v>
+        <v>1.07</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="O31" t="n">
-        <v>3.7</v>
+        <v>3.16</v>
       </c>
       <c r="P31" t="n">
-        <v>4.5</v>
+        <v>4.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5657,61 +5657,61 @@
         <v>2.11</v>
       </c>
       <c r="O33" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P33" t="n">
         <v>2.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AB33" t="n">
         <v>2.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6134,61 +6134,61 @@
         <v>3.61</v>
       </c>
       <c r="O36" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P36" t="n">
         <v>1.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA36" t="n">
         <v>1.57</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.35</v>
+        <v>2.14</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="O37" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P37" t="n">
-        <v>4.4</v>
+        <v>4.24</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA37" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB37" t="n">
         <v>1.8</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="O39" t="n">
         <v>2.7</v>
       </c>
       <c r="P39" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AA39" t="n">
         <v>3.1</v>
       </c>
       <c r="AB39" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6776,10 +6776,10 @@
         <v>3.29</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -6800,31 +6800,31 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6932,58 +6932,58 @@
         <v>2.62</v>
       </c>
       <c r="P41" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AA41" t="n">
         <v>3.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7094,55 +7094,55 @@
         <v>2.62</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.23</v>
+        <v>2.32</v>
       </c>
       <c r="O43" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="P43" t="n">
-        <v>2.29</v>
+        <v>3.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T44" t="n">
         <v>2.32</v>
       </c>
-      <c r="O44" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,68 +7558,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.5</v>
+        <v>1.52</v>
       </c>
       <c r="O46" t="n">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>2.57</v>
+        <v>5</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA46" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>3.09</v>
       </c>
       <c r="P47" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="R47" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S47" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="T47" t="n">
-        <v>3.32</v>
+        <v>2.59</v>
       </c>
       <c r="U47" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="V47" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="W47" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.65</v>
+        <v>3.08</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.3</v>
+        <v>3.42</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AK47" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,17 +8194,17 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,16 +8231,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="O50" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="P50" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="O51" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P51" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE51" t="n">
         <v>1.25</v>
       </c>
-      <c r="O51" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="P51" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,65 +8834,65 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.98</v>
+        <v>3.44</v>
       </c>
       <c r="O53" t="n">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="P53" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="R53" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="S53" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T53" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="U53" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="V53" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="W53" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X53" t="n">
         <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="Z53" t="n">
-        <v>5.4</v>
+        <v>3.48</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.52</v>
+        <v>1.88</v>
       </c>
       <c r="AC53" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG53" t="n">
         <v>2.12</v>
       </c>
-      <c r="AD53" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="O54" t="n">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="P54" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.95</v>
+        <v>2.52</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O55" t="n">
         <v>2.87</v>
@@ -9161,55 +9161,55 @@
         <v>3.93</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA55" t="n">
         <v>2.1</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.39</v>
+        <v>4.25</v>
       </c>
       <c r="O56" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P56" t="n">
-        <v>2.63</v>
+        <v>1.72</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9479,55 +9479,55 @@
         <v>4.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>4.25</v>
+        <v>2.39</v>
       </c>
       <c r="O58" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P58" t="n">
-        <v>1.72</v>
+        <v>2.63</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9797,55 +9797,55 @@
         <v>6.28</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA59" t="n">
         <v>1.75</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -9947,7 +9947,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O60" t="n">
         <v>3.48</v>
@@ -9956,55 +9956,55 @@
         <v>4.4</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB60" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK60" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,64 +10106,64 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="O61" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="P61" t="n">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10176,10 +10176,10 @@
         </is>
       </c>
       <c r="AJ61" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK61" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,80 +10265,80 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O62" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P62" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA62" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK62" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>0</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="O63" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="P63" t="n">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10742,64 +10742,64 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="O65" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="P65" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10901,64 +10901,64 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O66" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P66" t="n">
         <v>3.4</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -10971,10 +10971,10 @@
         </is>
       </c>
       <c r="AJ66" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK66" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>
@@ -11066,58 +11066,58 @@
         <v>3.26</v>
       </c>
       <c r="P67" t="n">
-        <v>2.98</v>
+        <v>3.32</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AA67" t="n">
         <v>1.95</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL67" t="n">
         <v>0</v>
@@ -11222,61 +11222,61 @@
         <v>1.67</v>
       </c>
       <c r="O68" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="P68" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11289,10 +11289,10 @@
         </is>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL68" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O2" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="P2" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="O3" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="P3" t="n">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="P11" t="n">
-        <v>4.27</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.96</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.97</v>
+        <v>3.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="P12" t="n">
-        <v>2.7</v>
+        <v>4.27</v>
       </c>
       <c r="Q12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.88</v>
       </c>
-      <c r="R12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
       <c r="U12" t="n">
-        <v>2.38</v>
+        <v>2.96</v>
       </c>
       <c r="V12" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC12" t="n">
         <v>3.7</v>
       </c>
-      <c r="AA12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U15" t="n">
         <v>2.18</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="O21" t="n">
-        <v>3.54</v>
+        <v>2.95</v>
       </c>
       <c r="P21" t="n">
-        <v>2.41</v>
+        <v>3.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,19 +4223,19 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>6.38</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>1.42</v>
+        <v>2.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -4244,10 +4244,10 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -4256,31 +4256,31 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,19 +4382,19 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.88</v>
+        <v>6.38</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.35</v>
+        <v>1.42</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4415,31 +4415,31 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4550,55 +4550,55 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.88</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U26" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="V26" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.12</v>
+        <v>1.63</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,80 +4700,80 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Q27" t="n">
-        <v>9.449999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="R27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T27" t="n">
-        <v>3.08</v>
+        <v>2.82</v>
       </c>
       <c r="U27" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="V27" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>3.42</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.14</v>
       </c>
-      <c r="AF27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK27" t="n">
-        <v>1.01</v>
+        <v>2.65</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="R28" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.35</v>
       </c>
-      <c r="T28" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.03</v>
+        <v>1.58</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.69</v>
+        <v>2.12</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,19 +5177,19 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -5198,10 +5198,10 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -5210,31 +5210,31 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,19 +5495,19 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -5516,10 +5516,10 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -5528,31 +5528,31 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="O42" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="P42" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="R42" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="S42" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="T42" t="n">
-        <v>2.74</v>
+        <v>2.12</v>
       </c>
       <c r="U42" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="W42" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.35</v>
+        <v>2.11</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.97</v>
+        <v>2.92</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.05</v>
+        <v>5.95</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.98</v>
+        <v>1.52</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T43" t="n">
         <v>2.32</v>
       </c>
-      <c r="O43" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.12</v>
-      </c>
       <c r="U43" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X43" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="AD43" t="n">
         <v>1.07</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="O44" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="P44" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.48</v>
+        <v>2.82</v>
       </c>
       <c r="R44" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="S44" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="T44" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="U44" t="n">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="V44" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="W44" t="n">
         <v>1.04</v>
       </c>
       <c r="X44" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.27</v>
+        <v>3.35</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.87</v>
+        <v>1.97</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="AC44" t="n">
-        <v>5.75</v>
+        <v>3.05</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,80 +7562,80 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.68</v>
+        <v>1.84</v>
       </c>
       <c r="O45" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="P45" t="n">
-        <v>2.95</v>
+        <v>4.35</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.74</v>
+        <v>2.54</v>
       </c>
       <c r="R45" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="S45" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK45" t="n">
         <v>1.78</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1.36</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>3.09</v>
       </c>
       <c r="P46" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="R46" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S46" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="T46" t="n">
-        <v>3.32</v>
+        <v>2.59</v>
       </c>
       <c r="U46" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="V46" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="W46" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X46" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.65</v>
+        <v>3.08</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.3</v>
+        <v>3.42</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O47" t="n">
         <v>2.5</v>
       </c>
-      <c r="O47" t="n">
-        <v>3.09</v>
-      </c>
       <c r="P47" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="R47" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="S47" t="n">
-        <v>1.43</v>
+        <v>1.78</v>
       </c>
       <c r="T47" t="n">
-        <v>2.59</v>
+        <v>2.01</v>
       </c>
       <c r="U47" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="V47" t="n">
-        <v>1.37</v>
+        <v>1.17</v>
       </c>
       <c r="W47" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X47" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.08</v>
+        <v>2</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.04</v>
+        <v>3.6</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.42</v>
+        <v>6.95</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.76</v>
+        <v>2.51</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.98</v>
+        <v>1.46</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK47" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="O48" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.54</v>
+        <v>2.1</v>
       </c>
       <c r="R48" t="n">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="S48" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="T48" t="n">
-        <v>2.32</v>
+        <v>3.32</v>
       </c>
       <c r="U48" t="n">
-        <v>3.28</v>
+        <v>2.27</v>
       </c>
       <c r="V48" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X48" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.56</v>
+        <v>4.65</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="AC48" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.66</v>
+        <v>2.18</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,68 +8671,68 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,68 +8989,68 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.01</v>
+        <v>4.25</v>
       </c>
       <c r="O55" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="P55" t="n">
-        <v>3.93</v>
+        <v>1.72</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>4.25</v>
+        <v>2.39</v>
       </c>
       <c r="O56" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P56" t="n">
-        <v>1.72</v>
+        <v>2.63</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,64 +9629,64 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.39</v>
+        <v>2.01</v>
       </c>
       <c r="O58" t="n">
-        <v>3.22</v>
+        <v>2.87</v>
       </c>
       <c r="P58" t="n">
-        <v>2.63</v>
+        <v>3.93</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,64 +9788,64 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="O59" t="n">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="P59" t="n">
-        <v>6.28</v>
+        <v>4.4</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="R59" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="S59" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T59" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U59" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="V59" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W59" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X59" t="n">
         <v>1.01</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z59" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK59" t="n">
-        <v>2.41</v>
+        <v>1.94</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,64 +9947,64 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="O60" t="n">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="P60" t="n">
-        <v>4.4</v>
+        <v>6.28</v>
       </c>
       <c r="Q60" t="n">
+        <v>2</v>
+      </c>
+      <c r="R60" t="n">
         <v>2.26</v>
       </c>
-      <c r="R60" t="n">
-        <v>2.14</v>
-      </c>
       <c r="S60" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T60" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U60" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="V60" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W60" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X60" t="n">
         <v>1.01</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z60" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.94</v>
+        <v>2.41</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,64 +10742,64 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O65" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="P65" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="R65" t="n">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="S65" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="T65" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="U65" t="n">
-        <v>2.33</v>
+        <v>3.15</v>
       </c>
       <c r="V65" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="W65" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X65" t="n">
         <v>1.01</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="Z65" t="n">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.12</v>
+        <v>1.69</v>
       </c>
       <c r="AC65" t="n">
-        <v>2.48</v>
+        <v>3.77</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG65" t="n">
-        <v>2.27</v>
+        <v>1.84</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="AJ65" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,64 +10901,64 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="O66" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="P66" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="R66" t="n">
-        <v>2.01</v>
+        <v>2.24</v>
       </c>
       <c r="S66" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="T66" t="n">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="U66" t="n">
-        <v>3.15</v>
+        <v>2.33</v>
       </c>
       <c r="V66" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="W66" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X66" t="n">
         <v>1.01</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.07</v>
+        <v>1.64</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.69</v>
+        <v>2.12</v>
       </c>
       <c r="AC66" t="n">
-        <v>3.77</v>
+        <v>2.48</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.84</v>
+        <v>2.27</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -10971,10 +10971,10 @@
         </is>
       </c>
       <c r="AJ66" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="O2" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="P2" t="n">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O3" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="P3" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="O5" t="n">
-        <v>3.34</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.98</v>
+        <v>5.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.65</v>
+        <v>1.94</v>
       </c>
       <c r="R5" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>3.04</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="W5" t="n">
         <v>1.11</v>
@@ -1235,31 +1235,31 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.92</v>
+        <v>5.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>2.19</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.57</v>
+        <v>2.43</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.44</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.59</v>
       </c>
       <c r="W6" t="n">
         <v>1.11</v>
@@ -1394,31 +1394,31 @@
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.1</v>
       </c>
-      <c r="Z6" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>9.5</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.17</v>
       </c>
-      <c r="Q10" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.16</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="O11" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7</v>
+        <v>4.27</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.88</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
-        <v>2.38</v>
+        <v>2.96</v>
       </c>
       <c r="V11" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC11" t="n">
         <v>3.7</v>
       </c>
-      <c r="AA11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="P12" t="n">
-        <v>4.27</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.96</v>
+        <v>2.38</v>
       </c>
       <c r="V12" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.97</v>
+        <v>3.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>9.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="P13" t="n">
-        <v>3.03</v>
+        <v>1.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.55</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U13" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.58</v>
+        <v>1.02</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="O21" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U22" t="n">
         <v>2.18</v>
       </c>
-      <c r="O22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,19 +4223,19 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.88</v>
+        <v>6.38</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.35</v>
+        <v>1.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -4244,10 +4244,10 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -4256,31 +4256,31 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,19 +4382,19 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>6.38</v>
+        <v>2.88</v>
       </c>
       <c r="O25" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>1.42</v>
+        <v>2.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4415,31 +4415,31 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4550,55 +4550,55 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.449999999999999</v>
+        <v>2.88</v>
       </c>
       <c r="R26" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="S26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="V26" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.63</v>
+        <v>2.12</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.43</v>
       </c>
-      <c r="O27" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="P27" t="n">
-        <v>7.47</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.65</v>
+        <v>1.01</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="R28" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U28" t="n">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="V28" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.58</v>
+        <v>2.03</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.12</v>
+        <v>1.69</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.44</v>
+        <v>2.65</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,19 +5018,19 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -5039,10 +5039,10 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -5051,31 +5051,31 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,19 +5177,19 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -5198,10 +5198,10 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -5210,31 +5210,31 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,65 +5336,65 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="O31" t="n">
-        <v>3.16</v>
+        <v>3.7</v>
       </c>
       <c r="P31" t="n">
-        <v>4.24</v>
+        <v>4.53</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="R31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG31" t="n">
         <v>2</v>
       </c>
-      <c r="S31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>6.76</v>
+        <v>1.82</v>
       </c>
       <c r="O32" t="n">
-        <v>4.4</v>
+        <v>3.16</v>
       </c>
       <c r="P32" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z32" t="n">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.5</v>
+        <v>2.29</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.67</v>
+        <v>2.06</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.07</v>
+        <v>1.8</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="O42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T42" t="n">
         <v>2.74</v>
       </c>
-      <c r="P42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.12</v>
-      </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="V42" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X42" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.11</v>
+        <v>3.35</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.92</v>
+        <v>1.97</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.31</v>
+        <v>1.81</v>
       </c>
       <c r="AC42" t="n">
-        <v>5.95</v>
+        <v>3.05</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="O43" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="P43" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="R43" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="S43" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="T43" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="U43" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AC43" t="n">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="AD43" t="n">
         <v>1.07</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="O44" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P44" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.82</v>
+        <v>3.48</v>
       </c>
       <c r="R44" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="S44" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="T44" t="n">
-        <v>2.74</v>
+        <v>2.32</v>
       </c>
       <c r="U44" t="n">
-        <v>2.82</v>
+        <v>3.9</v>
       </c>
       <c r="V44" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="W44" t="n">
         <v>1.04</v>
       </c>
       <c r="X44" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.35</v>
+        <v>2.27</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.97</v>
+        <v>2.87</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.81</v>
+        <v>1.4</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.05</v>
+        <v>5.75</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.72</v>
+        <v>2.19</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.98</v>
+        <v>1.59</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,68 +7717,68 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,80 +7880,80 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.68</v>
+        <v>1.52</v>
       </c>
       <c r="O47" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>2.95</v>
+        <v>5</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.74</v>
+        <v>2.1</v>
       </c>
       <c r="R47" t="n">
-        <v>1.65</v>
+        <v>2.31</v>
       </c>
       <c r="S47" t="n">
-        <v>1.78</v>
+        <v>1.26</v>
       </c>
       <c r="T47" t="n">
-        <v>2.01</v>
+        <v>3.32</v>
       </c>
       <c r="U47" t="n">
-        <v>4.5</v>
+        <v>2.27</v>
       </c>
       <c r="V47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47" t="n">
         <v>1.17</v>
       </c>
-      <c r="W47" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK47" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>3.09</v>
       </c>
       <c r="P48" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="R48" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="S48" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="T48" t="n">
-        <v>3.32</v>
+        <v>2.59</v>
       </c>
       <c r="U48" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="V48" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="W48" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X48" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.65</v>
+        <v>3.08</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.3</v>
+        <v>3.42</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,68 +8194,68 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>4.25</v>
+        <v>2.39</v>
       </c>
       <c r="O55" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P55" t="n">
-        <v>1.72</v>
+        <v>2.63</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.39</v>
+        <v>4.25</v>
       </c>
       <c r="O56" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P56" t="n">
-        <v>2.63</v>
+        <v>1.72</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,64 +10106,64 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.92</v>
+        <v>1.25</v>
       </c>
       <c r="O61" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="P61" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10176,10 +10176,10 @@
         </is>
       </c>
       <c r="AJ61" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK61" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,64 +10265,64 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="O62" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P62" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="R62" t="n">
-        <v>1.94</v>
+        <v>2.29</v>
       </c>
       <c r="S62" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="T62" t="n">
-        <v>2.79</v>
+        <v>2.96</v>
       </c>
       <c r="U62" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="V62" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W62" t="n">
         <v>1.06</v>
       </c>
       <c r="X62" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.97</v>
+        <v>3.7</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AC62" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="AJ62" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,64 +10424,64 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="O63" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="P63" t="n">
-        <v>9</v>
+        <v>3.64</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,64 +10742,64 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="O65" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="P65" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="R65" t="n">
-        <v>2.01</v>
+        <v>2.24</v>
       </c>
       <c r="S65" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="T65" t="n">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="U65" t="n">
-        <v>3.15</v>
+        <v>2.33</v>
       </c>
       <c r="V65" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="W65" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X65" t="n">
         <v>1.01</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.07</v>
+        <v>1.64</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.69</v>
+        <v>2.12</v>
       </c>
       <c r="AC65" t="n">
-        <v>3.77</v>
+        <v>2.48</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.84</v>
+        <v>2.27</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="AJ65" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,64 +10901,64 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O66" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="P66" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="R66" t="n">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="S66" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="T66" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="U66" t="n">
-        <v>2.33</v>
+        <v>3.15</v>
       </c>
       <c r="V66" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="W66" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X66" t="n">
         <v>1.01</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="Z66" t="n">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.12</v>
+        <v>1.69</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.48</v>
+        <v>3.77</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG66" t="n">
-        <v>2.27</v>
+        <v>1.84</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -10971,10 +10971,10 @@
         </is>
       </c>
       <c r="AJ66" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="O2" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="P2" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="O3" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="P3" t="n">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P10" t="n">
-        <v>3.03</v>
+        <v>4.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="R10" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>2.25</v>
+        <v>2.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>4</v>
+        <v>2.97</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.58</v>
+        <v>2.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.43</v>
+        <v>3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.81</v>
+        <v>9.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>4.27</v>
+        <v>1.17</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.28</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.96</v>
+        <v>1.99</v>
       </c>
       <c r="V11" t="n">
-        <v>1.32</v>
+        <v>1.71</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.97</v>
+        <v>5.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.06</v>
+        <v>1.36</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="AF11" t="n">
         <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.93</v>
+        <v>1.02</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="R12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
         <v>2.25</v>
       </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.38</v>
-      </c>
       <c r="V12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.45</v>
       </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>9.5</v>
+        <v>2.32</v>
       </c>
       <c r="O13" t="n">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="P13" t="n">
-        <v>1.17</v>
+        <v>2.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.949999999999999</v>
+        <v>2.88</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="S13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.99</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.9</v>
+        <v>3.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,19 +5018,19 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -5039,10 +5039,10 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -5051,31 +5051,31 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,19 +5177,19 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -5198,10 +5198,10 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -5210,31 +5210,31 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,80 +6767,80 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="O40" t="n">
-        <v>3.55</v>
+        <v>2.62</v>
       </c>
       <c r="P40" t="n">
-        <v>3.29</v>
+        <v>3.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.43</v>
+        <v>3.34</v>
       </c>
       <c r="R40" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U40" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="V40" t="n">
-        <v>1.49</v>
+        <v>1.14</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.17</v>
+        <v>1.74</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.1</v>
+        <v>2.02</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.6</v>
+        <v>3.34</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.48</v>
+        <v>5.75</v>
       </c>
       <c r="AD40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK40" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.64</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="O41" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="P41" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="R41" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="S41" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="V41" t="n">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.71</v>
+        <v>1.17</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.12</v>
+        <v>4.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="AC41" t="n">
-        <v>5.75</v>
+        <v>2.48</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="O42" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="P42" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.82</v>
+        <v>3.32</v>
       </c>
       <c r="R42" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="S42" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="T42" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="U42" t="n">
-        <v>2.82</v>
+        <v>3.75</v>
       </c>
       <c r="V42" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="W42" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.35</v>
+        <v>2.31</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="AC42" t="n">
-        <v>3.05</v>
+        <v>5.75</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK42" t="n">
         <v>1.44</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="O43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T43" t="n">
         <v>2.74</v>
       </c>
-      <c r="P43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.12</v>
-      </c>
       <c r="U43" t="n">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X43" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.11</v>
+        <v>3.35</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.92</v>
+        <v>1.97</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.31</v>
+        <v>1.81</v>
       </c>
       <c r="AC43" t="n">
-        <v>5.95</v>
+        <v>3.05</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="O44" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="P44" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="R44" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="S44" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="T44" t="n">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="U44" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="V44" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W44" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AC44" t="n">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="AD44" t="n">
         <v>1.07</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.84</v>
+        <v>2.75</v>
       </c>
       <c r="O45" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="P45" t="n">
-        <v>4.35</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="R45" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z45" t="n">
         <v>1.95</v>
       </c>
-      <c r="S45" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U45" t="n">
+      <c r="AA45" t="n">
         <v>3.28</v>
       </c>
-      <c r="V45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AB45" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.6</v>
+        <v>6.95</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.04</v>
+        <v>2.51</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,68 +7717,68 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,68 +7876,68 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="O48" t="n">
-        <v>3.09</v>
+        <v>3.94</v>
       </c>
       <c r="P48" t="n">
-        <v>2.5</v>
+        <v>5.21</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.25</v>
+        <v>2.07</v>
       </c>
       <c r="R48" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S48" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T48" t="n">
-        <v>2.59</v>
+        <v>3.5</v>
       </c>
       <c r="U48" t="n">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="V48" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="W48" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X48" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.08</v>
+        <v>4.65</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.04</v>
+        <v>1.55</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AC48" t="n">
-        <v>3.42</v>
+        <v>2.3</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.4</v>
+        <v>2.24</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,80 +8198,80 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.68</v>
+        <v>1.84</v>
       </c>
       <c r="O49" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="P49" t="n">
-        <v>2.95</v>
+        <v>4.35</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.74</v>
+        <v>2.54</v>
       </c>
       <c r="R49" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="S49" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK49" t="n">
         <v>1.78</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1.36</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8363,7 +8363,7 @@
         <v>2.75</v>
       </c>
       <c r="P50" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O52" t="n">
         <v>3.55</v>
@@ -8687,31 +8687,31 @@
         <v>4</v>
       </c>
       <c r="R52" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S52" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T52" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="U52" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="V52" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W52" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X52" t="n">
         <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z52" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="AA52" t="n">
         <v>1.41</v>
@@ -8720,19 +8720,19 @@
         <v>2.52</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,68 +8830,68 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,68 +8989,68 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9479,43 +9479,43 @@
         <v>4.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="R57" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S57" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="T57" t="n">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="U57" t="n">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="V57" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W57" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X57" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AC57" t="n">
-        <v>4.61</v>
+        <v>4.51</v>
       </c>
       <c r="AD57" t="n">
         <v>1.18</v>
@@ -9527,7 +9527,7 @@
         <v>2.17</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9629,65 +9629,65 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="O58" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="P58" t="n">
-        <v>3.93</v>
+        <v>3.35</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R58" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="S58" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="T58" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="U58" t="n">
-        <v>2.96</v>
+        <v>2.71</v>
       </c>
       <c r="V58" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W58" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X58" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA58" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG58" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB58" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH58" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,25 +9788,25 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="O59" t="n">
-        <v>3.48</v>
+        <v>4.4</v>
       </c>
       <c r="P59" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="R59" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="S59" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T59" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U59" t="n">
         <v>2.63</v>
@@ -9815,37 +9815,37 @@
         <v>1.44</v>
       </c>
       <c r="W59" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X59" t="n">
         <v>1.01</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z59" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,64 +9947,64 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="O60" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P60" t="n">
         <v>4</v>
       </c>
-      <c r="P60" t="n">
-        <v>6.28</v>
-      </c>
       <c r="Q60" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="R60" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="S60" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T60" t="n">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U60" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="V60" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W60" t="n">
         <v>1.07</v>
       </c>
       <c r="X60" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z60" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB60" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AE60" t="n">
         <v>1.11</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK60" t="n">
-        <v>2.41</v>
+        <v>1.91</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,80 +10265,80 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="O62" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P62" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="R62" t="n">
-        <v>2.29</v>
+        <v>1.94</v>
       </c>
       <c r="S62" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="T62" t="n">
-        <v>2.96</v>
+        <v>2.79</v>
       </c>
       <c r="U62" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="V62" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W62" t="n">
         <v>1.06</v>
       </c>
       <c r="X62" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z62" t="n">
-        <v>3.7</v>
+        <v>2.97</v>
       </c>
       <c r="AA62" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK62" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE62" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF62" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG62" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>1.84</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,64 +10424,64 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="O63" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P63" t="n">
-        <v>3.64</v>
+        <v>2.82</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="R63" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="S63" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T63" t="n">
-        <v>2.79</v>
+        <v>3.2</v>
       </c>
       <c r="U63" t="n">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="V63" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W63" t="n">
         <v>1.06</v>
       </c>
       <c r="X63" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.97</v>
+        <v>3.58</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AC63" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="AJ63" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,64 +10742,64 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O65" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="P65" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="R65" t="n">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="S65" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T65" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U65" t="n">
-        <v>2.33</v>
+        <v>2.96</v>
       </c>
       <c r="V65" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="W65" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X65" t="n">
         <v>1.01</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="Z65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.64</v>
+        <v>2.07</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.12</v>
+        <v>1.63</v>
       </c>
       <c r="AC65" t="n">
-        <v>2.48</v>
+        <v>3.77</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG65" t="n">
-        <v>2.27</v>
+        <v>1.84</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="AJ65" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,64 +10901,64 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="O66" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="P66" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="R66" t="n">
-        <v>2.01</v>
+        <v>2.24</v>
       </c>
       <c r="S66" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="T66" t="n">
-        <v>2.74</v>
+        <v>3.15</v>
       </c>
       <c r="U66" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="V66" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="W66" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X66" t="n">
         <v>1.01</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.07</v>
+        <v>1.58</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.69</v>
+        <v>2.12</v>
       </c>
       <c r="AC66" t="n">
-        <v>3.77</v>
+        <v>2.48</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -10971,10 +10971,10 @@
         </is>
       </c>
       <c r="AJ66" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>
@@ -11060,22 +11060,22 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="O67" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="P67" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="Q67" t="n">
         <v>2.63</v>
       </c>
       <c r="R67" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S67" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T67" t="n">
         <v>2.77</v>
@@ -11084,40 +11084,40 @@
         <v>2.7</v>
       </c>
       <c r="V67" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W67" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X67" t="n">
         <v>1.01</v>
       </c>
       <c r="Y67" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD67" t="n">
         <v>1.31</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>1.27</v>
       </c>
       <c r="AE67" t="n">
         <v>1.07</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="AJ67" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AL67" t="n">
         <v>0</v>
@@ -11219,64 +11219,64 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="O68" t="n">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="P68" t="n">
-        <v>4.16</v>
+        <v>4.75</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="R68" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S68" t="n">
         <v>1.25</v>
       </c>
       <c r="T68" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U68" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="V68" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W68" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X68" t="n">
         <v>1.01</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z68" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="AA68" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF68" t="n">
         <v>1.59</v>
       </c>
-      <c r="AB68" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AG68" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11289,10 +11289,10 @@
         </is>
       </c>
       <c r="AJ68" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK68" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="AL68" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O2" t="n">
         <v>3.34</v>
       </c>
       <c r="P2" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -887,10 +887,10 @@
         <v>2.13</v>
       </c>
       <c r="O3" t="n">
-        <v>3.36</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1211,22 +1211,22 @@
         <v>5.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="R5" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
         <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="W5" t="n">
         <v>1.11</v>
@@ -1241,25 +1241,25 @@
         <v>5.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="AD5" t="n">
         <v>1.59</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1532,13 +1532,13 @@
         <v>4.75</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
         <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U7" t="n">
         <v>2.29</v>
@@ -1547,7 +1547,7 @@
         <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
@@ -1565,10 +1565,10 @@
         <v>2.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="n">
         <v>1.15</v>
@@ -1577,7 +1577,7 @@
         <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O8" t="n">
         <v>3.5</v>
@@ -1688,7 +1688,7 @@
         <v>3.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R8" t="n">
         <v>2.2</v>
@@ -1697,46 +1697,46 @@
         <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="V8" t="n">
         <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
         <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
         <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="O9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P9" t="n">
         <v>3.55</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3.68</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,65 +1997,65 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>4.27</v>
+        <v>3.14</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG10" t="n">
         <v>2.28</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,16 +2156,16 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
         <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.949999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="R11" t="n">
         <v>3.2</v>
@@ -2177,22 +2177,22 @@
         <v>4.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="V11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
         <v>1.36</v>
@@ -2201,19 +2201,19 @@
         <v>3.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
         <v>1.79</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P12" t="n">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="O13" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="P13" t="n">
-        <v>2.7</v>
+        <v>4.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="R13" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>2.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2636,22 +2636,22 @@
         <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R14" t="n">
         <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="U14" t="n">
         <v>2.92</v>
@@ -2660,7 +2660,7 @@
         <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
         <v>1</v>
@@ -2669,16 +2669,16 @@
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
         <v>2.02</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="AD14" t="n">
         <v>1.21</v>
@@ -2687,10 +2687,10 @@
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2804,7 +2804,7 @@
         <v>2.88</v>
       </c>
       <c r="R15" t="n">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="S15" t="n">
         <v>1.24</v>
@@ -2816,10 +2816,10 @@
         <v>2.18</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
@@ -2834,22 +2834,22 @@
         <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.21</v>
+        <v>2.43</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK15" t="n">
         <v>1.44</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.52</v>
+        <v>6.38</v>
       </c>
       <c r="O23" t="n">
-        <v>3.44</v>
+        <v>4.3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.65</v>
+        <v>1.42</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.06</v>
+        <v>5.5</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="S23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="V23" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.34</v>
+        <v>2.28</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.48</v>
+        <v>1.07</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,19 +4223,19 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>6.38</v>
+        <v>2.88</v>
       </c>
       <c r="O24" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>1.42</v>
+        <v>2.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -4244,10 +4244,10 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -4256,31 +4256,31 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U25" t="n">
         <v>2.88</v>
       </c>
-      <c r="O25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Q27" t="n">
-        <v>9.449999999999999</v>
+        <v>1.93</v>
       </c>
       <c r="R27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T27" t="n">
-        <v>3.08</v>
+        <v>2.82</v>
       </c>
       <c r="U27" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="V27" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>3.42</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.01</v>
+        <v>2.65</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.8</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R28" t="n">
         <v>2.4</v>
       </c>
       <c r="S28" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T28" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="U28" t="n">
-        <v>2.74</v>
+        <v>2.36</v>
       </c>
       <c r="V28" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.54</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.88</v>
+        <v>2.23</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.65</v>
+        <v>1.03</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>6.76</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>4.4</v>
+        <v>3.06</v>
       </c>
       <c r="P29" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z29" t="n">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.5</v>
+        <v>2.27</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.07</v>
+        <v>1.78</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,19 +5336,19 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -5357,10 +5357,10 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -5369,31 +5369,31 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,65 +5495,65 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="O32" t="n">
-        <v>3.16</v>
+        <v>3.7</v>
       </c>
       <c r="P32" t="n">
-        <v>4.24</v>
+        <v>4.53</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="R32" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG32" t="n">
         <v>2</v>
       </c>
-      <c r="S32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.11</v>
+        <v>6.75</v>
       </c>
       <c r="O33" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.75</v>
+        <v>1.43</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.75</v>
+        <v>6.28</v>
       </c>
       <c r="R33" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="S33" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T33" t="n">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="U33" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="V33" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W33" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB33" t="n">
         <v>2.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.59</v>
+        <v>1.07</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6131,34 +6131,34 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="O36" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P36" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
         <v>2.31</v>
       </c>
       <c r="S36" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T36" t="n">
         <v>3.32</v>
       </c>
       <c r="U36" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="V36" t="n">
         <v>1.52</v>
       </c>
       <c r="W36" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X36" t="n">
         <v>1</v>
@@ -6173,19 +6173,19 @@
         <v>1.57</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE36" t="n">
         <v>1.16</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG36" t="n">
         <v>2.34</v>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="O37" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P37" t="n">
-        <v>4.24</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="R37" t="n">
         <v>2.06</v>
       </c>
       <c r="S37" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T37" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U37" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="V37" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W37" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
         <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AD37" t="n">
         <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF37" t="n">
         <v>1.86</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="O40" t="n">
-        <v>2.62</v>
+        <v>3.54</v>
       </c>
       <c r="P40" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.34</v>
+        <v>2.55</v>
       </c>
       <c r="R40" t="n">
-        <v>1.78</v>
+        <v>2.23</v>
       </c>
       <c r="S40" t="n">
-        <v>1.69</v>
+        <v>1.28</v>
       </c>
       <c r="T40" t="n">
-        <v>2.04</v>
+        <v>3.18</v>
       </c>
       <c r="U40" t="n">
-        <v>4</v>
+        <v>2.41</v>
       </c>
       <c r="V40" t="n">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.74</v>
+        <v>1.16</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.02</v>
+        <v>4.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.34</v>
+        <v>1.64</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.3</v>
+        <v>2.12</v>
       </c>
       <c r="AC40" t="n">
-        <v>5.75</v>
+        <v>2.56</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,80 +6926,80 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.97</v>
+        <v>2.34</v>
       </c>
       <c r="O41" t="n">
-        <v>3.55</v>
+        <v>2.69</v>
       </c>
       <c r="P41" t="n">
-        <v>3.29</v>
+        <v>3.05</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.43</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U41" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="V41" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.17</v>
+        <v>1.71</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.1</v>
+        <v>2.02</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.48</v>
+        <v>6.75</v>
       </c>
       <c r="AD41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41" t="n">
         <v>1.44</v>
       </c>
-      <c r="AE41" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK41" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="O42" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="P42" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.32</v>
+        <v>3.37</v>
       </c>
       <c r="R42" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S42" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="T42" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="U42" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="V42" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AB42" t="n">
         <v>1.36</v>
       </c>
       <c r="AC42" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AE42" t="n">
         <v>1.03</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O43" t="n">
         <v>3.2</v>
@@ -7253,25 +7253,25 @@
         <v>2.62</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="R43" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T43" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="U43" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="V43" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W43" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X43" t="n">
         <v>1.06</v>
@@ -7289,19 +7289,19 @@
         <v>1.81</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.05</v>
+        <v>3.43</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE43" t="n">
         <v>1.1</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>1.25</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7412,22 +7412,22 @@
         <v>3.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.1</v>
+        <v>3.51</v>
       </c>
       <c r="R44" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="S44" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="T44" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="U44" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V44" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W44" t="n">
         <v>1.03</v>
@@ -7436,10 +7436,10 @@
         <v>1.16</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AA44" t="n">
         <v>2.92</v>
@@ -7448,7 +7448,7 @@
         <v>1.31</v>
       </c>
       <c r="AC44" t="n">
-        <v>5.95</v>
+        <v>5.1</v>
       </c>
       <c r="AD44" t="n">
         <v>1.07</v>
@@ -7457,10 +7457,10 @@
         <v>1.02</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="O45" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P45" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Q45" t="n">
         <v>2.5</v>
       </c>
-      <c r="P45" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.6</v>
-      </c>
       <c r="R45" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="S45" t="n">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="T45" t="n">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="U45" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="V45" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="W45" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.28</v>
+        <v>2.31</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AC45" t="n">
-        <v>6.95</v>
+        <v>4.2</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.51</v>
+        <v>2.18</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="O46" t="n">
-        <v>3.09</v>
+        <v>2.57</v>
       </c>
       <c r="P46" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.25</v>
+        <v>3.84</v>
       </c>
       <c r="R46" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="S46" t="n">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="T46" t="n">
-        <v>2.59</v>
+        <v>2.01</v>
       </c>
       <c r="U46" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="V46" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="W46" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.29</v>
+        <v>1.76</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.08</v>
+        <v>1.95</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.04</v>
+        <v>3.28</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.42</v>
+        <v>6.95</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.76</v>
+        <v>2.35</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.98</v>
+        <v>1.49</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK46" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,68 +7876,68 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,68 +8035,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="O49" t="n">
-        <v>3.05</v>
+        <v>3.94</v>
       </c>
       <c r="P49" t="n">
-        <v>4.35</v>
+        <v>5</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.54</v>
+        <v>2.07</v>
       </c>
       <c r="R49" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="S49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="V49" t="n">
         <v>1.52</v>
       </c>
-      <c r="T49" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U49" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.25</v>
-      </c>
       <c r="W49" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X49" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.56</v>
+        <v>4.65</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.53</v>
+        <v>2.29</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.15</v>
+        <v>1.49</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O50" t="n">
         <v>2.75</v>
       </c>
       <c r="P50" t="n">
-        <v>3.95</v>
+        <v>4.09</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8516,31 +8516,31 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O51" t="n">
-        <v>5.3</v>
+        <v>5.65</v>
       </c>
       <c r="P51" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="R51" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="S51" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T51" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U51" t="n">
         <v>2.2</v>
       </c>
       <c r="V51" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W51" t="n">
         <v>1.16</v>
@@ -8549,31 +8549,31 @@
         <v>1.02</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z51" t="n">
         <v>5.32</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AK51" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,80 +8675,80 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="O52" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P52" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R52" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S52" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="T52" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="U52" t="n">
-        <v>2.13</v>
+        <v>2.59</v>
       </c>
       <c r="V52" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="W52" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X52" t="n">
         <v>1.01</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z52" t="n">
-        <v>5.45</v>
+        <v>3.48</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.52</v>
+        <v>1.88</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.11</v>
+        <v>2.97</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="AE52" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK52" t="n">
         <v>1.23</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>1.14</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="O54" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P54" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="R54" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S54" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T54" t="n">
-        <v>2.91</v>
+        <v>4</v>
       </c>
       <c r="U54" t="n">
-        <v>2.59</v>
+        <v>2.05</v>
       </c>
       <c r="V54" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="W54" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X54" t="n">
         <v>1.01</v>
       </c>
       <c r="Y54" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE54" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z54" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF54" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>4.25</v>
+        <v>1.9</v>
       </c>
       <c r="O56" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P56" t="n">
-        <v>1.72</v>
+        <v>4.2</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,64 +9470,64 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1.9</v>
+        <v>4.25</v>
       </c>
       <c r="O57" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P57" t="n">
-        <v>4.2</v>
+        <v>1.72</v>
       </c>
       <c r="Q57" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U57" t="n">
         <v>2.75</v>
       </c>
-      <c r="R57" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="S57" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U57" t="n">
-        <v>3.34</v>
-      </c>
       <c r="V57" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="W57" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="X57" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="AC57" t="n">
-        <v>4.51</v>
+        <v>3.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE57" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.66</v>
+        <v>1.15</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9641,19 +9641,19 @@
         <v>2.7</v>
       </c>
       <c r="R58" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S58" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T58" t="n">
         <v>2.78</v>
       </c>
       <c r="U58" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="V58" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W58" t="n">
         <v>1.1</v>
@@ -9662,31 +9662,31 @@
         <v>1</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z58" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="AA58" t="n">
         <v>1.98</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AC58" t="n">
         <v>3.5</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG58" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK58" t="n">
         <v>1.62</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,80 +9788,80 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="O59" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="P59" t="n">
-        <v>5.8</v>
+        <v>4.05</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="R59" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S59" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T59" t="n">
         <v>3.2</v>
       </c>
       <c r="U59" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V59" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W59" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X59" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y59" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ59" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z59" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG59" t="n">
+      <c r="AK59" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ59" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>2.28</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,64 +9947,64 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="O60" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="P60" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="R60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U60" t="n">
         <v>2.18</v>
       </c>
-      <c r="S60" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T60" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U60" t="n">
-        <v>2.63</v>
-      </c>
       <c r="V60" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W60" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X60" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z60" t="n">
-        <v>3.55</v>
+        <v>4.09</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.94</v>
+        <v>2.11</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AG60" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,64 +10106,64 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="O61" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="P61" t="n">
-        <v>9</v>
+        <v>3.75</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10176,10 +10176,10 @@
         </is>
       </c>
       <c r="AJ61" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,64 +10265,64 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="O62" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P62" t="n">
-        <v>3.64</v>
+        <v>2.82</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="R62" t="n">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="S62" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T62" t="n">
-        <v>2.79</v>
+        <v>3.08</v>
       </c>
       <c r="U62" t="n">
-        <v>2.99</v>
+        <v>2.43</v>
       </c>
       <c r="V62" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W62" t="n">
         <v>1.06</v>
       </c>
       <c r="X62" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.97</v>
+        <v>3.55</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AC62" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="AJ62" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,80 +10424,80 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.18</v>
+        <v>1.34</v>
       </c>
       <c r="O63" t="n">
-        <v>3.5</v>
+        <v>5.16</v>
       </c>
       <c r="P63" t="n">
-        <v>2.82</v>
+        <v>6.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="R63" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="S63" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T63" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="U63" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="V63" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W63" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X63" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z63" t="n">
-        <v>3.58</v>
+        <v>4.6</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.94</v>
+        <v>2.33</v>
       </c>
       <c r="AC63" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK63" t="n">
         <v>2.88</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>1.57</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10751,46 +10751,46 @@
         <v>3.4</v>
       </c>
       <c r="Q65" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T65" t="n">
         <v>2.55</v>
-      </c>
-      <c r="R65" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T65" t="n">
-        <v>2.75</v>
       </c>
       <c r="U65" t="n">
         <v>2.96</v>
       </c>
       <c r="V65" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W65" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X65" t="n">
         <v>1.01</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z65" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA65" t="n">
         <v>2.07</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AC65" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE65" t="n">
         <v>1.03</v>
@@ -10799,7 +10799,7 @@
         <v>1.85</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>1.25</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10901,64 +10901,64 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="O66" t="n">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="P66" t="n">
-        <v>3.24</v>
+        <v>2.87</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="R66" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="S66" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="T66" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="U66" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="V66" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W66" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X66" t="n">
         <v>1.01</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z66" t="n">
-        <v>4.1</v>
+        <v>5.02</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AB66" t="n">
         <v>2.12</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG66" t="n">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         </is>
       </c>
       <c r="AJ66" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK66" t="n">
         <v>1.67</v>
@@ -11063,19 +11063,19 @@
         <v>2.04</v>
       </c>
       <c r="O67" t="n">
-        <v>3.35</v>
+        <v>3.26</v>
       </c>
       <c r="P67" t="n">
         <v>3.3</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="R67" t="n">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="S67" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T67" t="n">
         <v>2.77</v>
@@ -11084,10 +11084,10 @@
         <v>2.7</v>
       </c>
       <c r="V67" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W67" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X67" t="n">
         <v>1.01</v>
@@ -11099,25 +11099,25 @@
         <v>3.2</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC67" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF67" t="n">
         <v>1.73</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="AJ67" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK67" t="n">
         <v>1.63</v>
@@ -11225,10 +11225,10 @@
         <v>4.1</v>
       </c>
       <c r="P68" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R68" t="n">
         <v>2.4</v>
@@ -11237,10 +11237,10 @@
         <v>1.25</v>
       </c>
       <c r="T68" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U68" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="V68" t="n">
         <v>1.57</v>
@@ -11252,25 +11252,25 @@
         <v>1.01</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z68" t="n">
-        <v>4.68</v>
+        <v>4.4</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AC68" t="n">
         <v>2.47</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF68" t="n">
         <v>1.59</v>
@@ -11289,10 +11289,10 @@
         </is>
       </c>
       <c r="AJ68" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK68" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL68" t="n">
         <v>0</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU68"/>
+  <dimension ref="A1:AU69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O9" t="n">
         <v>3.5</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="O10" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC10" t="n">
         <v>3.5</v>
       </c>
-      <c r="P10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.28</v>
+        <v>1.81</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
+        <v>2.32</v>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.14</v>
+        <v>2.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.6</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.2</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="O12" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="R12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
         <v>2.25</v>
       </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.38</v>
-      </c>
       <c r="V12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.45</v>
       </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AE12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA12" t="n">
+      <c r="AK12" t="n">
         <v>1.68</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.44</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.81</v>
+        <v>11</v>
       </c>
       <c r="O13" t="n">
-        <v>3.58</v>
+        <v>7</v>
       </c>
       <c r="P13" t="n">
-        <v>4.27</v>
+        <v>1.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.28</v>
+        <v>11.6</v>
       </c>
       <c r="R13" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
-        <v>2.66</v>
+        <v>4.5</v>
       </c>
       <c r="U13" t="n">
-        <v>2.96</v>
+        <v>2.03</v>
       </c>
       <c r="V13" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.06</v>
+        <v>1.36</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.93</v>
+        <v>1.02</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.18</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U24" t="n">
         <v>2.88</v>
       </c>
-      <c r="O24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="O25" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.88</v>
+        <v>1.93</v>
       </c>
       <c r="R26" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U26" t="n">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="V26" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.44</v>
+        <v>2.65</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.93</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R27" t="n">
         <v>2.4</v>
       </c>
       <c r="S27" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T27" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>2.74</v>
+        <v>2.36</v>
       </c>
       <c r="V27" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.88</v>
+        <v>2.23</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.65</v>
+        <v>1.03</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4868,71 +4868,71 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>9.449999999999999</v>
+        <v>2.88</v>
       </c>
       <c r="R28" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="V28" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK28" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.03</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O29" t="n">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="P29" t="n">
-        <v>3.63</v>
+        <v>2.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R29" t="n">
-        <v>1.92</v>
+        <v>2.45</v>
       </c>
       <c r="S29" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="T29" t="n">
-        <v>2.36</v>
+        <v>3.5</v>
       </c>
       <c r="U29" t="n">
-        <v>3.28</v>
+        <v>2.29</v>
       </c>
       <c r="V29" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF29" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z29" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AG29" t="n">
-        <v>1.57</v>
+        <v>2.42</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,19 +5336,19 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -5357,10 +5357,10 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -5369,31 +5369,31 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.67</v>
+        <v>6.75</v>
       </c>
       <c r="O32" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="P32" t="n">
-        <v>4.53</v>
+        <v>1.43</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.14</v>
+        <v>6.28</v>
       </c>
       <c r="R32" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U32" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="V32" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.65</v>
+        <v>2.27</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG32" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.98</v>
+        <v>1.07</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>6.75</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>4.4</v>
+        <v>3.06</v>
       </c>
       <c r="P33" t="n">
-        <v>1.43</v>
+        <v>3.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.28</v>
+        <v>2.6</v>
       </c>
       <c r="R33" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="S33" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="T33" t="n">
-        <v>3.75</v>
+        <v>2.36</v>
       </c>
       <c r="U33" t="n">
-        <v>2.15</v>
+        <v>3.28</v>
       </c>
       <c r="V33" t="n">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.53</v>
+        <v>2.27</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.27</v>
+        <v>4.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.71</v>
+        <v>2.17</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.07</v>
+        <v>1.78</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6561,12 +6561,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6711,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="AU39" s="3" t="n">
-        <v>46186.58333333334</v>
+        <v>46186.60416666666</v>
       </c>
     </row>
     <row r="40">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.99</v>
+        <v>2.37</v>
       </c>
       <c r="O40" t="n">
-        <v>3.54</v>
+        <v>2.7</v>
       </c>
       <c r="P40" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="R40" t="n">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="S40" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="T40" t="n">
-        <v>3.18</v>
+        <v>2.04</v>
       </c>
       <c r="U40" t="n">
-        <v>2.41</v>
+        <v>4.33</v>
       </c>
       <c r="V40" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="W40" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.16</v>
+        <v>1.71</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.2</v>
+        <v>2.02</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.64</v>
+        <v>3.4</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.56</v>
+        <v>6.75</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="O41" t="n">
-        <v>2.69</v>
+        <v>3.54</v>
       </c>
       <c r="P41" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="R41" t="n">
-        <v>1.73</v>
+        <v>2.23</v>
       </c>
       <c r="S41" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="T41" t="n">
-        <v>2.04</v>
+        <v>3.18</v>
       </c>
       <c r="U41" t="n">
-        <v>4.33</v>
+        <v>2.41</v>
       </c>
       <c r="V41" t="n">
-        <v>1.2</v>
+        <v>1.49</v>
       </c>
       <c r="W41" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.71</v>
+        <v>1.16</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.02</v>
+        <v>4.2</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.4</v>
+        <v>1.64</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.75</v>
+        <v>2.56</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7085,16 +7085,16 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="O42" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P42" t="n">
-        <v>2.68</v>
+        <v>2.95</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="R42" t="n">
         <v>1.85</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="O43" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="P43" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.95</v>
+        <v>3.51</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S43" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="T43" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="U43" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.35</v>
+        <v>2.11</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.97</v>
+        <v>2.92</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.43</v>
+        <v>5.1</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="O44" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="P44" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.51</v>
+        <v>2.95</v>
       </c>
       <c r="R44" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S44" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="T44" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="U44" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="V44" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="W44" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X44" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.11</v>
+        <v>3.35</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.92</v>
+        <v>1.97</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.31</v>
+        <v>1.81</v>
       </c>
       <c r="AC44" t="n">
-        <v>5.1</v>
+        <v>3.43</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.54</v>
+        <v>1.95</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7515,12 +7515,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.84</v>
+        <v>2.31</v>
       </c>
       <c r="O45" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P45" t="n">
         <v>3.05</v>
       </c>
-      <c r="P45" t="n">
-        <v>4.35</v>
-      </c>
       <c r="Q45" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="R45" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="S45" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="T45" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="U45" t="n">
-        <v>3.28</v>
+        <v>4.3</v>
       </c>
       <c r="V45" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="W45" t="n">
         <v>1.03</v>
       </c>
       <c r="X45" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AU45" s="3" t="n">
-        <v>46186.66666666666</v>
+        <v>46186.64583333334</v>
       </c>
     </row>
     <row r="46">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,68 +7717,68 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,68 +8035,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P49" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB49" t="n">
         <v>1.53</v>
       </c>
-      <c r="O49" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="P49" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="R49" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U49" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>2.29</v>
-      </c>
       <c r="AC49" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK49" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="O50" t="n">
-        <v>2.75</v>
+        <v>3.94</v>
       </c>
       <c r="P50" t="n">
-        <v>4.09</v>
+        <v>5</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.68</v>
+        <v>1.12</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.05</v>
+        <v>4.65</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.4</v>
+        <v>1.55</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.33</v>
+        <v>2.29</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AU50" s="3" t="n">
-        <v>46186.70833333334</v>
+        <v>46186.66666666666</v>
       </c>
     </row>
     <row r="51">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cobresal</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.25</v>
+        <v>2.11</v>
       </c>
       <c r="O51" t="n">
-        <v>5.65</v>
+        <v>2.75</v>
       </c>
       <c r="P51" t="n">
-        <v>8.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.15</v>
+        <v>1.68</v>
       </c>
       <c r="Z51" t="n">
-        <v>5.32</v>
+        <v>2.05</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.47</v>
+        <v>3.4</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.6</v>
+        <v>1.33</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="AU51" s="3" t="n">
-        <v>46186.77083333334</v>
+        <v>46186.70833333334</v>
       </c>
     </row>
     <row r="52">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Cobresal</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,81 +8675,81 @@
         </is>
       </c>
       <c r="N52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O52" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="P52" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X52" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK52" t="n">
         <v>3.5</v>
       </c>
-      <c r="O52" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R52" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S52" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T52" t="n">
-        <v>3</v>
-      </c>
-      <c r="U52" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AL52" t="n">
         <v>0</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>0</v>
       </c>
       <c r="AU52" s="3" t="n">
-        <v>46186.79166666666</v>
+        <v>46186.77083333334</v>
       </c>
     </row>
     <row r="53">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,68 +8830,68 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,68 +8989,68 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>3.5</v>
       </c>
       <c r="O55" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="P55" t="n">
-        <v>2.63</v>
+        <v>1.98</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA55" t="n">
         <v>1.85</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="AU55" s="3" t="n">
-        <v>46186.83333333334</v>
+        <v>46186.79166666666</v>
       </c>
     </row>
     <row r="56">
@@ -9320,10 +9320,10 @@
         <v>4.2</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="R56" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="S56" t="n">
         <v>1.53</v>
@@ -9350,7 +9350,7 @@
         <v>2.62</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="AB56" t="n">
         <v>1.48</v>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,64 +9470,64 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>4.25</v>
+        <v>2.05</v>
       </c>
       <c r="O57" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P57" t="n">
-        <v>1.72</v>
+        <v>3.36</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="R57" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S57" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T57" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U57" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="V57" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W57" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X57" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>1.25</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,64 +9629,64 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.06</v>
+        <v>2.39</v>
       </c>
       <c r="O58" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P58" t="n">
-        <v>3.35</v>
+        <v>2.63</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,64 +9788,64 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1.74</v>
+        <v>5.11</v>
       </c>
       <c r="O59" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P59" t="n">
-        <v>4.05</v>
+        <v>1.58</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.27</v>
+        <v>5.53</v>
       </c>
       <c r="R59" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="S59" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T59" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X59" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z59" t="n">
         <v>3.2</v>
       </c>
-      <c r="U59" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AA59" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.9</v>
+        <v>1.14</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AU59" s="3" t="n">
-        <v>46186.85416666666</v>
+        <v>46186.83333333334</v>
       </c>
     </row>
     <row r="60">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,64 +9947,64 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="O60" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="P60" t="n">
-        <v>5.9</v>
+        <v>4.05</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="R60" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S60" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="T60" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="U60" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="V60" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="W60" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X60" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="Z60" t="n">
-        <v>4.09</v>
+        <v>2.92</v>
       </c>
       <c r="AA60" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF60" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB60" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG60" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK60" t="n">
-        <v>2.7</v>
+        <v>1.84</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,64 +10106,64 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="O61" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P61" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="Q61" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R61" t="n">
         <v>2.5</v>
       </c>
-      <c r="R61" t="n">
-        <v>1.94</v>
-      </c>
       <c r="S61" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T61" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="U61" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="V61" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W61" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X61" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y61" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD61" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z61" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE61" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG61" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10176,10 +10176,10 @@
         </is>
       </c>
       <c r="AJ61" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK61" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AL61" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>46186.875</v>
+        <v>46186.85416666666</v>
       </c>
     </row>
     <row r="62">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,64 +10265,64 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="O62" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P62" t="n">
-        <v>2.82</v>
+        <v>3.75</v>
       </c>
       <c r="Q62" t="n">
         <v>2.5</v>
       </c>
       <c r="R62" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="S62" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T62" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="U62" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="V62" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="W62" t="n">
         <v>1.06</v>
       </c>
       <c r="X62" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z62" t="n">
-        <v>3.55</v>
+        <v>2.97</v>
       </c>
       <c r="AA62" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB62" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB62" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AC62" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AE62" t="n">
         <v>1.11</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG62" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="AJ62" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,80 +10424,80 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.34</v>
+        <v>2.18</v>
       </c>
       <c r="O63" t="n">
-        <v>5.16</v>
+        <v>3.5</v>
       </c>
       <c r="P63" t="n">
-        <v>6.5</v>
+        <v>2.82</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.8</v>
+        <v>2.46</v>
       </c>
       <c r="R63" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="S63" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X63" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63" t="n">
         <v>1.22</v>
       </c>
-      <c r="T63" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U63" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X63" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AK63" t="n">
-        <v>2.88</v>
+        <v>1.69</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10536,12 +10536,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10579,68 +10579,68 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10653,10 +10653,10 @@
         </is>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AL64" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>46186.89583333334</v>
+        <v>46186.875</v>
       </c>
     </row>
     <row r="65">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10738,68 +10738,68 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="AJ65" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10845,7 +10845,7 @@
         <v>0</v>
       </c>
       <c r="AU65" s="3" t="n">
-        <v>46186.91666666666</v>
+        <v>46186.89583333334</v>
       </c>
     </row>
     <row r="66">
@@ -10913,19 +10913,19 @@
         <v>2.43</v>
       </c>
       <c r="R66" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="S66" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T66" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="U66" t="n">
         <v>2.23</v>
       </c>
       <c r="V66" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W66" t="n">
         <v>1.14</v>
@@ -10934,31 +10934,31 @@
         <v>1.01</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z66" t="n">
-        <v>5.02</v>
+        <v>4.6</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF66" t="n">
         <v>1.53</v>
       </c>
       <c r="AG66" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,64 +11060,64 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="O67" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P67" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="R67" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="S67" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T67" t="n">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="U67" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="V67" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W67" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X67" t="n">
         <v>1.01</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z67" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AC67" t="n">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="AJ67" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AL67" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>46186.9375</v>
+        <v>46186.91666666666</v>
       </c>
     </row>
     <row r="68">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,109 +11219,268 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="O68" t="n">
-        <v>4.1</v>
+        <v>3.26</v>
       </c>
       <c r="P68" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q68" t="n">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="R68" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="S68" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T68" t="n">
-        <v>3.42</v>
+        <v>2.77</v>
       </c>
       <c r="U68" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="V68" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="W68" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X68" t="n">
         <v>1.01</v>
       </c>
       <c r="Y68" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" s="3" t="n">
+        <v>46186.9375</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Miami FC II</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O69" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2</v>
+      </c>
+      <c r="R69" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y69" t="n">
         <v>1.15</v>
       </c>
-      <c r="Z68" t="n">
+      <c r="Z69" t="n">
         <v>4.4</v>
       </c>
-      <c r="AA68" t="n">
+      <c r="AA69" t="n">
         <v>1.56</v>
       </c>
-      <c r="AB68" t="n">
+      <c r="AB69" t="n">
         <v>2.29</v>
       </c>
-      <c r="AC68" t="n">
+      <c r="AC69" t="n">
         <v>2.47</v>
       </c>
-      <c r="AD68" t="n">
+      <c r="AD69" t="n">
         <v>1.48</v>
       </c>
-      <c r="AE68" t="n">
+      <c r="AE69" t="n">
         <v>1.16</v>
       </c>
-      <c r="AF68" t="n">
+      <c r="AF69" t="n">
         <v>1.59</v>
       </c>
-      <c r="AG68" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68" t="n">
+      <c r="AG69" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69" t="n">
         <v>1.12</v>
       </c>
-      <c r="AK68" t="n">
+      <c r="AK69" t="n">
         <v>2.25</v>
       </c>
-      <c r="AL68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP68" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU68" s="3" t="n">
+      <c r="AL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" s="3" t="n">
         <v>46186.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="O2" t="n">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="P2" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>3.34</v>
       </c>
       <c r="P3" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="O4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P4" t="n">
         <v>3.4</v>
       </c>
-      <c r="P4" t="n">
-        <v>2.92</v>
-      </c>
       <c r="Q4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.81</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>4.27</v>
+        <v>1.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.28</v>
+        <v>11.6</v>
       </c>
       <c r="R10" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="T10" t="n">
-        <v>2.66</v>
+        <v>4.5</v>
       </c>
       <c r="U10" t="n">
-        <v>2.96</v>
+        <v>2.03</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.06</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.73</v>
+        <v>3.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.79</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.93</v>
+        <v>1.02</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="O12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC12" t="n">
         <v>3.5</v>
       </c>
-      <c r="P12" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.28</v>
+        <v>1.81</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>11</v>
+        <v>2.04</v>
       </c>
       <c r="O13" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.14</v>
+        <v>3.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.6</v>
+        <v>2.43</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.17</v>
       </c>
-      <c r="T13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W13" t="n">
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
         <v>1.2</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AK13" t="n">
-        <v>1.02</v>
+        <v>1.68</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6.38</v>
+        <v>2.53</v>
       </c>
       <c r="O23" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="P23" t="n">
-        <v>1.42</v>
+        <v>2.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>2.12</v>
+        <v>2.88</v>
       </c>
       <c r="V23" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.5</v>
+        <v>3.04</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.28</v>
+        <v>3.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,80 +4223,80 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.53</v>
+        <v>6.38</v>
       </c>
       <c r="O24" t="n">
-        <v>3.44</v>
+        <v>4.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.63</v>
+        <v>1.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="R24" t="n">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="S24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="V24" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK24" t="n">
         <v>1.07</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.34</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>7.47</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.93</v>
+        <v>2.88</v>
       </c>
       <c r="R26" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.35</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.88</v>
+        <v>1.93</v>
       </c>
       <c r="R28" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U28" t="n">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="V28" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.44</v>
+        <v>2.65</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="O29" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P29" t="n">
-        <v>2.75</v>
+        <v>4.53</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.63</v>
+        <v>2.14</v>
       </c>
       <c r="R29" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="S29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V29" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.13</v>
       </c>
-      <c r="Z29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AF29" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,19 +5336,19 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -5357,10 +5357,10 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -5369,31 +5369,31 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>6.75</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>4.4</v>
+        <v>3.06</v>
       </c>
       <c r="P32" t="n">
-        <v>1.43</v>
+        <v>3.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.28</v>
+        <v>2.6</v>
       </c>
       <c r="R32" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="S32" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="T32" t="n">
-        <v>3.75</v>
+        <v>2.36</v>
       </c>
       <c r="U32" t="n">
-        <v>2.15</v>
+        <v>3.28</v>
       </c>
       <c r="V32" t="n">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="W32" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.53</v>
+        <v>2.27</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.27</v>
+        <v>4.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.71</v>
+        <v>2.17</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.07</v>
+        <v>1.78</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O33" t="n">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="P33" t="n">
-        <v>3.63</v>
+        <v>2.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R33" t="n">
-        <v>1.92</v>
+        <v>2.45</v>
       </c>
       <c r="S33" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="T33" t="n">
-        <v>2.36</v>
+        <v>3.5</v>
       </c>
       <c r="U33" t="n">
-        <v>3.28</v>
+        <v>2.29</v>
       </c>
       <c r="V33" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="W33" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X33" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF33" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z33" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AG33" t="n">
-        <v>1.57</v>
+        <v>2.42</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,80 +7085,80 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="O42" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="P42" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="R42" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="S42" t="n">
         <v>1.55</v>
       </c>
       <c r="T42" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="U42" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.43</v>
+        <v>2.11</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.55</v>
+        <v>2.92</v>
       </c>
       <c r="AB42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC42" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AK42" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="O43" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="P43" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.51</v>
+        <v>2.95</v>
       </c>
       <c r="R43" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="T43" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="U43" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X43" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.11</v>
+        <v>3.35</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.92</v>
+        <v>1.97</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.31</v>
+        <v>1.81</v>
       </c>
       <c r="AC43" t="n">
-        <v>5.1</v>
+        <v>3.43</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.54</v>
+        <v>1.95</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="O44" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="P44" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="S44" t="n">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="T44" t="n">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="U44" t="n">
-        <v>2.95</v>
+        <v>4.3</v>
       </c>
       <c r="V44" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="W44" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.35</v>
+        <v>2.09</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.97</v>
+        <v>3.04</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.81</v>
+        <v>1.29</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.43</v>
+        <v>6.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="O45" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="P45" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="R45" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="S45" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="T45" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="U45" t="n">
-        <v>4.3</v>
+        <v>3.92</v>
       </c>
       <c r="V45" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="W45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE45" t="n">
         <v>1.03</v>
       </c>
-      <c r="X45" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF45" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,68 +7717,68 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,80 +7880,80 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="O47" t="n">
-        <v>3.1</v>
+        <v>2.57</v>
       </c>
       <c r="P47" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="R47" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="S47" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK47" t="n">
         <v>1.36</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U47" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,68 +8035,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,68 +8830,68 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,68 +8989,68 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O55" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P55" t="n">
         <v>1.98</v>
@@ -9167,16 +9167,16 @@
         <v>2.2</v>
       </c>
       <c r="S55" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T55" t="n">
         <v>3</v>
       </c>
       <c r="U55" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="V55" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W55" t="n">
         <v>1.06</v>
@@ -9200,7 +9200,7 @@
         <v>2.97</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE55" t="n">
         <v>1.12</v>
@@ -9225,7 +9225,7 @@
         <v>1.7</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.9</v>
+        <v>5.27</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>3.84</v>
       </c>
       <c r="P56" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="Q56" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U56" t="n">
         <v>2.75</v>
       </c>
-      <c r="R56" t="n">
-        <v>2</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U56" t="n">
-        <v>3.25</v>
-      </c>
       <c r="V56" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="W56" t="n">
         <v>1.04</v>
       </c>
       <c r="X56" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.33</v>
+        <v>1.89</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AC56" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AE56" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.73</v>
+        <v>1.14</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,80 +9470,80 @@
         </is>
       </c>
       <c r="N57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3</v>
+      </c>
+      <c r="P57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="n">
         <v>2.05</v>
       </c>
-      <c r="O57" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P57" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R57" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S57" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U57" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y57" t="n">
+      <c r="AG57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ57" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z57" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ57" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK57" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,64 +9788,64 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>5.11</v>
+        <v>2.07</v>
       </c>
       <c r="O59" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="P59" t="n">
-        <v>1.58</v>
+        <v>3.36</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.53</v>
+        <v>2.55</v>
       </c>
       <c r="R59" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="S59" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T59" t="n">
-        <v>2.91</v>
+        <v>2.74</v>
       </c>
       <c r="U59" t="n">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="V59" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W59" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X59" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z59" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC59" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,64 +9947,64 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="O60" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P60" t="n">
-        <v>4.05</v>
+        <v>5.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S60" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T60" t="n">
         <v>2.88</v>
       </c>
       <c r="U60" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="V60" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W60" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X60" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.92</v>
+        <v>3.57</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,64 +10106,64 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="O61" t="n">
-        <v>4.05</v>
+        <v>3.54</v>
       </c>
       <c r="P61" t="n">
-        <v>5.8</v>
+        <v>4.12</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.99</v>
+        <v>2.39</v>
       </c>
       <c r="R61" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="S61" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
+      </c>
+      <c r="V61" t="n">
         <v>1.33</v>
       </c>
-      <c r="T61" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U61" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1.4</v>
-      </c>
       <c r="W61" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X61" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z61" t="n">
-        <v>3.57</v>
+        <v>3.08</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.66</v>
+        <v>2.06</v>
       </c>
       <c r="AB61" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG61" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10176,10 +10176,10 @@
         </is>
       </c>
       <c r="AJ61" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK61" t="n">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="AL61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,64 +10265,64 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O62" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P62" t="n">
-        <v>3.75</v>
+        <v>2.82</v>
       </c>
       <c r="Q62" t="n">
         <v>2.5</v>
       </c>
       <c r="R62" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="S62" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="T62" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U62" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="V62" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X62" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD62" t="n">
         <v>1.32</v>
-      </c>
-      <c r="W62" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X62" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>1.22</v>
       </c>
       <c r="AE62" t="n">
         <v>1.11</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="AJ62" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,61 +10424,61 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.18</v>
+        <v>1.31</v>
       </c>
       <c r="O63" t="n">
-        <v>3.5</v>
+        <v>5.35</v>
       </c>
       <c r="P63" t="n">
-        <v>2.82</v>
+        <v>6.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.46</v>
+        <v>1.68</v>
       </c>
       <c r="R63" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="S63" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="T63" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="U63" t="n">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="V63" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="W63" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X63" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="Z63" t="n">
-        <v>3.58</v>
+        <v>4.8</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.89</v>
+        <v>2.52</v>
       </c>
       <c r="AC63" t="n">
-        <v>2.88</v>
+        <v>2.14</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG63" t="n">
         <v>2.07</v>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="AJ63" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.69</v>
+        <v>2.89</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,64 +10583,64 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.31</v>
+        <v>1.91</v>
       </c>
       <c r="O64" t="n">
-        <v>5.35</v>
+        <v>3.4</v>
       </c>
       <c r="P64" t="n">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="R64" t="n">
-        <v>2.7</v>
+        <v>1.94</v>
       </c>
       <c r="S64" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="T64" t="n">
-        <v>3.86</v>
+        <v>2.8</v>
       </c>
       <c r="U64" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="V64" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="W64" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X64" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="Z64" t="n">
-        <v>5.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.42</v>
+        <v>2.06</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.12</v>
+        <v>3.5</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10653,10 +10653,10 @@
         </is>
       </c>
       <c r="AJ64" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AK64" t="n">
-        <v>2.89</v>
+        <v>1.85</v>
       </c>
       <c r="AL64" t="n">
         <v>0</v>
@@ -10913,7 +10913,7 @@
         <v>2.43</v>
       </c>
       <c r="R66" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S66" t="n">
         <v>1.22</v>
@@ -10928,31 +10928,31 @@
         <v>1.59</v>
       </c>
       <c r="W66" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X66" t="n">
         <v>1.01</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z66" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF66" t="n">
         <v>1.53</v>
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="O67" t="n">
         <v>3.2</v>
       </c>
       <c r="P67" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q67" t="n">
         <v>2.9</v>
@@ -11081,13 +11081,13 @@
         <v>2.55</v>
       </c>
       <c r="U67" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="V67" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W67" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X67" t="n">
         <v>1.01</v>
@@ -11099,7 +11099,7 @@
         <v>2.85</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AB67" t="n">
         <v>1.64</v>
@@ -11133,7 +11133,7 @@
         <v>1.3</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AL67" t="n">
         <v>0</v>
@@ -11219,7 +11219,7 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="O68" t="n">
         <v>3.26</v>
@@ -11228,55 +11228,55 @@
         <v>3.3</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="R68" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="S68" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T68" t="n">
-        <v>2.77</v>
+        <v>3.09</v>
       </c>
       <c r="U68" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="V68" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W68" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X68" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z68" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA68" t="n">
         <v>1.89</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC68" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE68" t="n">
         <v>1.08</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG68" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>1.24</v>
       </c>
       <c r="AK68" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL68" t="n">
         <v>0</v>
@@ -11378,13 +11378,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O69" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P69" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="Q69" t="n">
         <v>2</v>
@@ -11405,7 +11405,7 @@
         <v>1.57</v>
       </c>
       <c r="W69" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X69" t="n">
         <v>1.01</v>

--- a/jogos_2026-06-13.xlsx
+++ b/jogos_2026-06-13.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,43 +725,43 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="O2" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA2" t="n">
         <v>1.7</v>
@@ -770,19 +770,19 @@
         <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,43 +884,43 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="O3" t="n">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>2.88</v>
+        <v>3.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA3" t="n">
         <v>1.75</v>
@@ -929,19 +929,19 @@
         <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+     